--- a/fangzheng_web_app/default_rules/transcode_agent/transcode_agent_rules.xlsx
+++ b/fangzheng_web_app/default_rules/transcode_agent/transcode_agent_rules.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W201"/>
+  <dimension ref="A1:W208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -630,9 +630,6 @@
           <t>NY3170HF</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
           <t>glue_code</t>
@@ -668,8 +665,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -717,14 +712,11 @@
           <t>尺寸:28*48；关键词:28*48</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>28*48</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>28*48</t>
@@ -765,8 +757,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -814,14 +804,11 @@
           <t>尺寸:27*48；关键词:27*48</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>27*48</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>27*48</t>
@@ -867,7 +854,6 @@
           <t>特殊需求内已给出映射，按原值保留</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -915,14 +901,11 @@
           <t>尺寸:24*48；关键词:24*48</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>24*48</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>24*48</t>
@@ -963,8 +946,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1012,14 +993,11 @@
           <t>尺寸:42*48；关键词:42*48</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>42*48</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>42*48</t>
@@ -1060,8 +1038,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1109,14 +1085,11 @@
           <t>尺寸:40*48；关键词:40*48</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>40*48</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>40*48</t>
@@ -1157,8 +1130,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1206,14 +1177,11 @@
           <t>尺寸:36*48；关键词:36*48</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>36*48</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>36*48</t>
@@ -1254,8 +1222,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1308,10 +1274,6 @@
           <t>NY-A2</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -1347,8 +1309,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1388,7 +1348,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>字段=胶系 | 目标=胶系代码 | 覆盖字段=glue_code | 覆盖值=AS | 条件=胶系:NY2150；关键词:NY2150 | 状态=可执行草稿</t>
+          <t>字段=胶系 | 目标=胶系代码 | 覆盖字段=glue_code | 覆盖值=2T | 条件=胶系:NY2150；关键词:NY2150 | 状态=可执行草稿</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1406,9 +1366,6 @@
           <t>NY2150</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
           <t>glue_code</t>
@@ -1416,7 +1373,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>AS</t>
+          <t>2T</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1444,8 +1401,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1493,15 +1448,11 @@
           <t>关键词:HVLP</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>HVLP</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
           <t>copper_type_code</t>
@@ -1537,8 +1488,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1591,10 +1540,6 @@
           <t>NY3150HC</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -1630,8 +1575,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1684,10 +1627,6 @@
           <t>NY-A1</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -1728,7 +1667,6 @@
           <t>特殊需求多条件同结果</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1781,10 +1719,6 @@
           <t>NY-A2</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -1825,7 +1759,6 @@
           <t>特殊需求多条件同结果</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1878,10 +1811,6 @@
           <t>NY3150HC</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
           <t>glue_code</t>
@@ -1922,7 +1851,6 @@
           <t>业务反馈列确认RV</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1962,7 +1890,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>字段=胶系 | 目标=胶系代码 | 覆盖字段=glue_code | 覆盖值=AS | 条件=胶系:NY2150；关键词:NY2150 | 状态=可执行草稿</t>
+          <t>字段=胶系 | 目标=胶系代码 | 覆盖字段=glue_code | 覆盖值=2T | 条件=胶系:NY2150；关键词:NY2150 | 状态=可执行草稿</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1980,9 +1908,6 @@
           <t>NY2150</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
           <t>glue_code</t>
@@ -1990,7 +1915,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>AS</t>
+          <t>2T</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -2018,8 +1943,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2077,9 +2000,6 @@
           <t>NY2150</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
           <t>glue_code</t>
@@ -2115,8 +2035,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2156,15 +2074,19 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>字段=基板厚度 | 目标=总厚/芯厚代码 | 覆盖字段=tc_code | 覆盖值=C | 状态=可执行草稿 | 依据=特殊需求明确写出全量芯厚口径</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>字段=基板厚度 | 目标=总厚/芯厚代码 | 覆盖字段=tc_code | 覆盖值=C | 条件=厚度:&lt;0.8 | 状态=可执行草稿 | 依据=特殊需求明确写出全量芯厚口径</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>厚度:&lt;0.8</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>&lt;0.8</t>
+        </is>
+      </c>
       <c r="O18" t="inlineStr">
         <is>
           <t>tc_code</t>
@@ -2182,7 +2104,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2202,10 +2124,9 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>特殊需求明确写出全量芯厚口径</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr"/>
+          <t>方正F7默认输入芯厚；&gt;=0.8mm由Agent总芯厚算法转总厚</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2253,15 +2174,11 @@
           <t>关键词:HS2-M2-VSP</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>HS2-M2-VSP</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
           <t>copper_type_code</t>
@@ -2297,8 +2214,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2346,15 +2261,11 @@
           <t>关键词:HS1-M2-VSP</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>HS1-M2-VSP</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
           <t>copper_type_code</t>
@@ -2390,8 +2301,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2449,9 +2358,6 @@
           <t>NY-A1</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
           <t>glue_code</t>
@@ -2487,8 +2393,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2536,7 +2440,6 @@
           <t>关键词:R/R</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>R/R</t>
@@ -2547,8 +2450,6 @@
           <t>R/R</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
           <t>copper_code</t>
@@ -2584,8 +2485,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2633,15 +2532,11 @@
           <t>关键词:当备注中有水印要求时</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>当备注中有水印要求时</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
           <t>copper_type_code</t>
@@ -2677,8 +2572,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2726,19 +2619,16 @@
           <t>厚度:0；关键词:当备注中有X0A0/X0B0/car/汽车板/458/439字样时</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>当备注中有X0A0/X0B0/car/汽车板/458/439字样时</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -2774,8 +2664,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2823,15 +2711,11 @@
           <t>关键词:当备注中有MINILED字样时</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>当备注中有MINILED字样时</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -2867,8 +2751,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2921,10 +2803,6 @@
           <t>NY3150HF</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -2960,8 +2838,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3014,10 +2890,6 @@
           <t>NY2140L</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -3053,8 +2925,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3112,9 +2982,6 @@
           <t>NY1140</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
           <t>glue_code</t>
@@ -3150,8 +3017,6 @@
           <t>21</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3199,19 +3064,16 @@
           <t>厚度:71；关键词:71(含)以下</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>71(含)以下</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
           <t>0.71</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
           <t>tc_code</t>
@@ -3247,8 +3109,6 @@
           <t>21</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3296,15 +3156,11 @@
           <t>厚度&gt;0.71</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
           <t>&gt;0.71</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
         <is>
           <t>tc_code</t>
@@ -3345,7 +3201,6 @@
           <t>旧特殊需求0.71以上总厚</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3388,12 +3243,6 @@
           <t>字段=基板厚度 | 目标=总厚/芯厚代码 | 覆盖字段=tc_code | 覆盖值=C | 状态=可执行草稿</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr">
         <is>
           <t>tc_code</t>
@@ -3429,8 +3278,6 @@
           <t>21</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3483,10 +3330,6 @@
           <t>NY2150</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -3527,7 +3370,6 @@
           <t>特殊需求多条件同结果</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3580,10 +3422,6 @@
           <t>NY2170</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -3624,7 +3462,6 @@
           <t>特殊需求多条件同结果</t>
         </is>
       </c>
-      <c r="W33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3677,10 +3514,6 @@
           <t>NY2150</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -3721,7 +3554,6 @@
           <t>特殊需求多条件同结果</t>
         </is>
       </c>
-      <c r="W34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3774,10 +3606,6 @@
           <t>NY2170</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -3818,7 +3646,6 @@
           <t>特殊需求多条件同结果</t>
         </is>
       </c>
-      <c r="W35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3876,9 +3703,6 @@
           <t>当胶系NY3150HF</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -3914,8 +3738,6 @@
           <t>27</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3963,11 +3785,6 @@
           <t>铜厚:F铜箔；关键词:当胶系</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr">
         <is>
           <t>copper_type_code</t>
@@ -4003,8 +3820,6 @@
           <t>28</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4052,15 +3867,11 @@
           <t>厚度:35</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
           <t>0.35</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr">
         <is>
           <t>copper_type_code</t>
@@ -4096,8 +3907,6 @@
           <t>28</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr"/>
-      <c r="W38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4155,9 +3964,6 @@
           <t>NY1140</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
         <is>
           <t>glue_code</t>
@@ -4193,8 +3999,6 @@
           <t>29</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr"/>
-      <c r="W39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4247,10 +4051,6 @@
           <t>NY2140</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -4286,8 +4086,6 @@
           <t>30</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr"/>
-      <c r="W40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4335,15 +4133,11 @@
           <t>关键词:5</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
         <is>
           <t>copper_code</t>
@@ -4379,8 +4173,6 @@
           <t>37</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr"/>
-      <c r="W41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4428,19 +4220,16 @@
           <t>厚度:0；关键词:当备注中有X0A0/X0B0/car/汽车板/458/439字样时</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
           <t>当备注中有X0A0/X0B0/car/汽车板/458/439字样时</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -4476,8 +4265,6 @@
           <t>37</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr"/>
-      <c r="W42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4525,15 +4312,11 @@
           <t>关键词:当备注中有MINILED字样时</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
           <t>当备注中有MINILED字样时</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -4569,8 +4352,6 @@
           <t>37</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr"/>
-      <c r="W43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4623,10 +4404,6 @@
           <t>NY3150HF</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -4662,8 +4439,6 @@
           <t>37</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr"/>
-      <c r="W44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4716,10 +4491,6 @@
           <t>NY2140L</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -4755,8 +4526,6 @@
           <t>37</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr"/>
-      <c r="W45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4804,15 +4573,11 @@
           <t>关键词:5</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
         <is>
           <t>copper_code</t>
@@ -4848,8 +4613,6 @@
           <t>38</t>
         </is>
       </c>
-      <c r="V46" t="inlineStr"/>
-      <c r="W46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4897,19 +4660,16 @@
           <t>厚度:0；关键词:当备注中有X0A0/X0B0/car/汽车板/458/439字样时</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
           <t>当备注中有X0A0/X0B0/car/汽车板/458/439字样时</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -4945,8 +4705,6 @@
           <t>38</t>
         </is>
       </c>
-      <c r="V47" t="inlineStr"/>
-      <c r="W47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4994,15 +4752,11 @@
           <t>关键词:当备注中有MINILED字样时</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
           <t>当备注中有MINILED字样时</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -5038,8 +4792,6 @@
           <t>38</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr"/>
-      <c r="W48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5092,10 +4844,6 @@
           <t>NY3150HF</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -5131,8 +4879,6 @@
           <t>38</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr"/>
-      <c r="W49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5185,10 +4931,6 @@
           <t>NY2140L</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -5224,8 +4966,6 @@
           <t>38</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr"/>
-      <c r="W50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5273,15 +5013,11 @@
           <t>关键词:HVLP</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
           <t>HVLP</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr">
         <is>
           <t>copper_type_code</t>
@@ -5317,8 +5053,6 @@
           <t>43</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr"/>
-      <c r="W51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5371,10 +5105,6 @@
           <t>NY3150HC</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -5410,8 +5140,6 @@
           <t>43</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr"/>
-      <c r="W52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5464,10 +5192,6 @@
           <t>NY-A1</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -5508,7 +5232,6 @@
           <t>特殊需求多条件同结果</t>
         </is>
       </c>
-      <c r="W53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5561,10 +5284,6 @@
           <t>NY-A2</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -5605,7 +5324,6 @@
           <t>特殊需求多条件同结果</t>
         </is>
       </c>
-      <c r="W54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5658,10 +5376,6 @@
           <t>NY3150HC</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr">
         <is>
           <t>glue_code</t>
@@ -5702,7 +5416,6 @@
           <t>业务反馈列确认RV</t>
         </is>
       </c>
-      <c r="W55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5760,9 +5473,6 @@
           <t>NY2150</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr">
         <is>
           <t>glue_code</t>
@@ -5798,8 +5508,6 @@
           <t>43</t>
         </is>
       </c>
-      <c r="V56" t="inlineStr"/>
-      <c r="W56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5847,15 +5555,11 @@
           <t>关键词:HVLP</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
           <t>HVLP</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr">
         <is>
           <t>copper_type_code</t>
@@ -5891,8 +5595,6 @@
           <t>44</t>
         </is>
       </c>
-      <c r="V57" t="inlineStr"/>
-      <c r="W57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5945,10 +5647,6 @@
           <t>NY3150HC</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -5984,8 +5682,6 @@
           <t>44</t>
         </is>
       </c>
-      <c r="V58" t="inlineStr"/>
-      <c r="W58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6038,10 +5734,6 @@
           <t>NY-A1</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -6082,7 +5774,6 @@
           <t>特殊需求多条件同结果</t>
         </is>
       </c>
-      <c r="W59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6135,10 +5826,6 @@
           <t>NY-A2</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -6179,7 +5866,6 @@
           <t>特殊需求多条件同结果</t>
         </is>
       </c>
-      <c r="W60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -6219,7 +5905,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>字段=胶系 | 目标=胶系代码 | 覆盖字段=glue_code | 覆盖值=2S | 条件=胶系:NY2150；关键词:NY2150 | 状态=可执行草稿</t>
+          <t>字段=胶系 | 目标=胶系代码 | 覆盖字段=glue_code | 覆盖值=2B | 条件=胶系:NY2150；关键词:NY2150 | 状态=可执行草稿</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6237,9 +5923,6 @@
           <t>NY2150</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr">
         <is>
           <t>glue_code</t>
@@ -6247,7 +5930,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>2S</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
@@ -6275,8 +5958,6 @@
           <t>44</t>
         </is>
       </c>
-      <c r="V61" t="inlineStr"/>
-      <c r="W61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -6324,15 +6005,11 @@
           <t>关键词:HVLP</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
           <t>HVLP</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr">
         <is>
           <t>copper_type_code</t>
@@ -6368,8 +6045,6 @@
           <t>45</t>
         </is>
       </c>
-      <c r="V62" t="inlineStr"/>
-      <c r="W62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6422,10 +6097,6 @@
           <t>NY3150HC</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -6461,8 +6132,6 @@
           <t>45</t>
         </is>
       </c>
-      <c r="V63" t="inlineStr"/>
-      <c r="W63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6515,10 +6184,6 @@
           <t>NY-A1</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -6559,7 +6224,6 @@
           <t>特殊需求多条件同结果</t>
         </is>
       </c>
-      <c r="W64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6612,10 +6276,6 @@
           <t>NY-A2</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -6656,7 +6316,6 @@
           <t>特殊需求多条件同结果</t>
         </is>
       </c>
-      <c r="W65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -6714,9 +6373,6 @@
           <t>NY2150</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr">
         <is>
           <t>glue_code</t>
@@ -6752,8 +6408,6 @@
           <t>45</t>
         </is>
       </c>
-      <c r="V66" t="inlineStr"/>
-      <c r="W66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -6801,15 +6455,11 @@
           <t>关键词:HVLP</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
           <t>HVLP</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr">
         <is>
           <t>copper_type_code</t>
@@ -6845,8 +6495,6 @@
           <t>46</t>
         </is>
       </c>
-      <c r="V67" t="inlineStr"/>
-      <c r="W67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6899,10 +6547,6 @@
           <t>NY3150HC</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -6938,8 +6582,6 @@
           <t>46</t>
         </is>
       </c>
-      <c r="V68" t="inlineStr"/>
-      <c r="W68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6987,11 +6629,6 @@
           <t>关键词:当胶系</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -7027,8 +6664,6 @@
           <t>46</t>
         </is>
       </c>
-      <c r="V69" t="inlineStr"/>
-      <c r="W69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -7081,10 +6716,6 @@
           <t>NY-A1</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -7125,7 +6756,6 @@
           <t>特殊需求多条件同结果</t>
         </is>
       </c>
-      <c r="W70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -7178,10 +6808,6 @@
           <t>NY-A2</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -7222,7 +6848,6 @@
           <t>特殊需求多条件同结果</t>
         </is>
       </c>
-      <c r="W71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -7280,9 +6905,6 @@
           <t>NY2150</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr">
         <is>
           <t>glue_code</t>
@@ -7318,8 +6940,6 @@
           <t>46</t>
         </is>
       </c>
-      <c r="V72" t="inlineStr"/>
-      <c r="W72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -7372,14 +6992,11 @@
           <t>NY2140</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
           <t>&gt;=0.8</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -7420,7 +7037,6 @@
           <t>特殊需求及引擎基板级别规则</t>
         </is>
       </c>
-      <c r="W73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -7473,14 +7089,11 @@
           <t>NY2140</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
           <t>&gt;=0.8</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -7521,7 +7134,6 @@
           <t>通用特殊规则及引擎基板级别规则</t>
         </is>
       </c>
-      <c r="W74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -7574,10 +7186,6 @@
           <t>NY2150H</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr">
         <is>
           <t>glue_code</t>
@@ -7613,8 +7221,6 @@
           <t>49</t>
         </is>
       </c>
-      <c r="V75" t="inlineStr"/>
-      <c r="W75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -7667,10 +7273,6 @@
           <t>NY2150H</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr">
         <is>
           <t>glue_code</t>
@@ -7706,8 +7308,6 @@
           <t>50</t>
         </is>
       </c>
-      <c r="V76" t="inlineStr"/>
-      <c r="W76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -7760,14 +7360,11 @@
           <t>NY2140</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
           <t>&gt;=0.8</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -7808,7 +7405,6 @@
           <t>特殊需求及引擎基板级别规则</t>
         </is>
       </c>
-      <c r="W77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -7861,14 +7457,11 @@
           <t>NY2140</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
           <t>&gt;=0.8</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -7909,7 +7502,6 @@
           <t>通用特殊规则及引擎基板级别规则</t>
         </is>
       </c>
-      <c r="W78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -7957,15 +7549,11 @@
           <t>关键词:HS1-M2-VSP</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
         <is>
           <t>HS1-M2-VSP</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr">
         <is>
           <t>copper_type_code</t>
@@ -8001,8 +7589,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="V79" t="inlineStr"/>
-      <c r="W79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -8050,15 +7636,11 @@
           <t>关键词:HS2-M2-VSP</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
           <t>HS2-M2-VSP</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr">
         <is>
           <t>copper_type_code</t>
@@ -8094,8 +7676,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="V80" t="inlineStr"/>
-      <c r="W80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -8143,15 +7723,11 @@
           <t>关键词:当客户规格描述有“AT板”字样时</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
           <t>当客户规格描述有“AT板”字样时</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -8187,8 +7763,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="V81" t="inlineStr"/>
-      <c r="W81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -8246,9 +7820,6 @@
           <t>NY2150</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr">
         <is>
           <t>glue_code</t>
@@ -8284,8 +7855,6 @@
           <t>101</t>
         </is>
       </c>
-      <c r="V82" t="inlineStr"/>
-      <c r="W82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -8333,15 +7902,11 @@
           <t>关键词:HS1-M2-VSP</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
         <is>
           <t>HS1-M2-VSP</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr">
         <is>
           <t>copper_type_code</t>
@@ -8377,8 +7942,6 @@
           <t>101</t>
         </is>
       </c>
-      <c r="V83" t="inlineStr"/>
-      <c r="W83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -8426,15 +7989,11 @@
           <t>关键词:HS2-M2-VSP</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
         <is>
           <t>HS2-M2-VSP</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr">
         <is>
           <t>copper_type_code</t>
@@ -8470,8 +8029,6 @@
           <t>101</t>
         </is>
       </c>
-      <c r="V84" t="inlineStr"/>
-      <c r="W84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -8519,15 +8076,11 @@
           <t>关键词:当客户规格描述有“AT板”字样时</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr">
         <is>
           <t>当客户规格描述有“AT板”字样时</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -8563,8 +8116,6 @@
           <t>101</t>
         </is>
       </c>
-      <c r="V85" t="inlineStr"/>
-      <c r="W85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -8612,7 +8163,6 @@
           <t>关键词:H/H</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
           <t>H/H</t>
@@ -8623,8 +8173,6 @@
           <t>H/H</t>
         </is>
       </c>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr">
         <is>
           <t>copper_code</t>
@@ -8660,8 +8208,6 @@
           <t>102</t>
         </is>
       </c>
-      <c r="V86" t="inlineStr"/>
-      <c r="W86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -8714,14 +8260,11 @@
           <t>NY2140</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
           <t>&gt;=0.8</t>
         </is>
       </c>
-      <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -8762,7 +8305,6 @@
           <t>特殊需求及引擎基板级别规则</t>
         </is>
       </c>
-      <c r="W87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -8815,14 +8357,11 @@
           <t>NY2140</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
           <t>&gt;=0.8</t>
         </is>
       </c>
-      <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -8863,7 +8402,6 @@
           <t>通用特殊规则及引擎基板级别规则</t>
         </is>
       </c>
-      <c r="W88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -8916,14 +8454,11 @@
           <t>NY2140</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
           <t>&gt;=0.8</t>
         </is>
       </c>
-      <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -8964,7 +8499,6 @@
           <t>特殊需求及引擎基板级别规则</t>
         </is>
       </c>
-      <c r="W89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -9017,14 +8551,11 @@
           <t>NY2140</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
           <t>&gt;=0.8</t>
         </is>
       </c>
-      <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -9065,7 +8596,6 @@
           <t>通用特殊规则及引擎基板级别规则</t>
         </is>
       </c>
-      <c r="W90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -9118,14 +8648,11 @@
           <t>NY2140</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr">
         <is>
           <t>&gt;=0.8</t>
         </is>
       </c>
-      <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -9166,7 +8693,6 @@
           <t>特殊需求及引擎基板级别规则</t>
         </is>
       </c>
-      <c r="W91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -9219,14 +8745,11 @@
           <t>NY2140</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr">
         <is>
           <t>&gt;=0.8</t>
         </is>
       </c>
-      <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -9267,7 +8790,6 @@
           <t>通用特殊规则及引擎基板级别规则</t>
         </is>
       </c>
-      <c r="W92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -9320,10 +8842,6 @@
           <t>NY3150HF</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -9359,8 +8877,6 @@
           <t>105</t>
         </is>
       </c>
-      <c r="V93" t="inlineStr"/>
-      <c r="W93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -9413,14 +8929,11 @@
           <t>NY2140</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
           <t>&gt;=0.8</t>
         </is>
       </c>
-      <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -9461,7 +8974,6 @@
           <t>特殊需求及引擎基板级别规则</t>
         </is>
       </c>
-      <c r="W94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -9514,14 +9026,11 @@
           <t>NY2140</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
           <t>&gt;=0.8</t>
         </is>
       </c>
-      <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -9562,7 +9071,6 @@
           <t>通用特殊规则及引擎基板级别规则</t>
         </is>
       </c>
-      <c r="W95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -9615,14 +9123,11 @@
           <t>NY2140</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
           <t>&gt;=0.8</t>
         </is>
       </c>
-      <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -9663,7 +9168,6 @@
           <t>特殊需求及引擎基板级别规则</t>
         </is>
       </c>
-      <c r="W96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -9716,14 +9220,11 @@
           <t>NY2140</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
         <is>
           <t>&gt;=0.8</t>
         </is>
       </c>
-      <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -9764,7 +9265,6 @@
           <t>通用特殊规则及引擎基板级别规则</t>
         </is>
       </c>
-      <c r="W97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -9812,19 +9312,16 @@
           <t>厚度:8；关键词:8mm时</t>
         </is>
       </c>
-      <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr">
         <is>
           <t>8mm时</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
           <t>0.8</t>
         </is>
       </c>
-      <c r="N98" t="inlineStr"/>
       <c r="O98" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -9860,8 +9357,6 @@
           <t>107</t>
         </is>
       </c>
-      <c r="V98" t="inlineStr"/>
-      <c r="W98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -9914,10 +9409,6 @@
           <t>NY2150</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
       <c r="O99" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -9958,7 +9449,6 @@
           <t>特殊需求多条件同结果</t>
         </is>
       </c>
-      <c r="W99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -10011,10 +9501,6 @@
           <t>NY2170</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -10055,7 +9541,6 @@
           <t>特殊需求多条件同结果</t>
         </is>
       </c>
-      <c r="W100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -10108,14 +9593,11 @@
           <t>NY2140</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr">
         <is>
           <t>&gt;=0.8</t>
         </is>
       </c>
-      <c r="N101" t="inlineStr"/>
       <c r="O101" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -10156,7 +9638,6 @@
           <t>特殊需求及引擎基板级别规则</t>
         </is>
       </c>
-      <c r="W101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -10209,14 +9690,11 @@
           <t>NY2140</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
           <t>&gt;=0.8</t>
         </is>
       </c>
-      <c r="N102" t="inlineStr"/>
       <c r="O102" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -10257,7 +9735,6 @@
           <t>通用特殊规则及引擎基板级别规则</t>
         </is>
       </c>
-      <c r="W102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -10310,10 +9787,6 @@
           <t>NY3150HF</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
       <c r="O103" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -10349,8 +9822,6 @@
           <t>108</t>
         </is>
       </c>
-      <c r="V103" t="inlineStr"/>
-      <c r="W103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -10403,10 +9874,6 @@
           <t>NY3150HF</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
       <c r="O104" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -10442,8 +9909,6 @@
           <t>109</t>
         </is>
       </c>
-      <c r="V104" t="inlineStr"/>
-      <c r="W104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -10496,10 +9961,6 @@
           <t>NY3150HF</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -10535,8 +9996,6 @@
           <t>110</t>
         </is>
       </c>
-      <c r="V105" t="inlineStr"/>
-      <c r="W105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -10589,10 +10048,6 @@
           <t>NY3150HF</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
       <c r="O106" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -10628,8 +10083,6 @@
           <t>111</t>
         </is>
       </c>
-      <c r="V106" t="inlineStr"/>
-      <c r="W106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -10682,10 +10135,6 @@
           <t>NY3150HF</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -10721,8 +10170,6 @@
           <t>112</t>
         </is>
       </c>
-      <c r="V107" t="inlineStr"/>
-      <c r="W107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -10775,10 +10222,6 @@
           <t>NY-A1</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
       <c r="O108" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -10814,8 +10257,6 @@
           <t>112</t>
         </is>
       </c>
-      <c r="V108" t="inlineStr"/>
-      <c r="W108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -10868,10 +10309,6 @@
           <t>NY3150HF</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -10907,8 +10344,6 @@
           <t>114</t>
         </is>
       </c>
-      <c r="V109" t="inlineStr"/>
-      <c r="W109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -10918,7 +10353,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -10956,11 +10391,6 @@
           <t>铜厚:1oz</t>
         </is>
       </c>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
       <c r="O110" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -10996,8 +10426,11 @@
           <t>116</t>
         </is>
       </c>
-      <c r="V110" t="inlineStr"/>
-      <c r="W110" t="inlineStr"/>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>停用拆分错误的1oz宽泛规则；由NY2140+厚度&gt;=0.8+铜厚&lt;1oz完整规则执行</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -11037,12 +10470,12 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=F1 | 条件=胶系:NY2140；厚度&gt;=0.8；铜厚&lt;=1oz | 状态=可执行草稿 | 依据=特殊需求及引擎基板级别规则</t>
+          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=F1 | 条件=胶系:NY2140；厚度&gt;=0.8；铜厚&lt;1oz | 状态=可执行草稿 | 依据=特殊需求及引擎基板级别规则</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>胶系:NY2140；厚度&gt;=0.8；铜厚&lt;=1oz</t>
+          <t>胶系:NY2140；厚度&gt;=0.8；铜厚&lt;1oz</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -11050,14 +10483,16 @@
           <t>NY2140</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>&lt;1oz</t>
+        </is>
+      </c>
       <c r="M111" t="inlineStr">
         <is>
           <t>&gt;=0.8</t>
         </is>
       </c>
-      <c r="N111" t="inlineStr"/>
       <c r="O111" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -11095,10 +10530,9 @@
       </c>
       <c r="V111" t="inlineStr">
         <is>
-          <t>特殊需求及引擎基板级别规则</t>
-        </is>
-      </c>
-      <c r="W111" t="inlineStr"/>
+          <t>特殊需求及引擎基板级别规则；业务确认：1oz以下不包含1oz</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -11108,7 +10542,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -11146,11 +10580,6 @@
           <t>铜厚:1oz</t>
         </is>
       </c>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -11186,8 +10615,11 @@
           <t>117</t>
         </is>
       </c>
-      <c r="V112" t="inlineStr"/>
-      <c r="W112" t="inlineStr"/>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>停用拆分错误的1oz宽泛规则；由NY2140+厚度&gt;=0.8+铜厚&lt;1oz完整规则执行</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -11227,12 +10659,12 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=F1 | 条件=胶系:NY2140；厚度&gt;=0.8；铜厚&lt;=1oz | 状态=可执行草稿 | 依据=特殊需求及引擎基板级别规则</t>
+          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=F1 | 条件=胶系:NY2140；厚度&gt;=0.8；铜厚&lt;1oz | 状态=可执行草稿 | 依据=特殊需求及引擎基板级别规则</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>胶系:NY2140；厚度&gt;=0.8；铜厚&lt;=1oz</t>
+          <t>胶系:NY2140；厚度&gt;=0.8；铜厚&lt;1oz</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -11240,14 +10672,16 @@
           <t>NY2140</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>&lt;1oz</t>
+        </is>
+      </c>
       <c r="M113" t="inlineStr">
         <is>
           <t>&gt;=0.8</t>
         </is>
       </c>
-      <c r="N113" t="inlineStr"/>
       <c r="O113" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -11285,10 +10719,9 @@
       </c>
       <c r="V113" t="inlineStr">
         <is>
-          <t>特殊需求及引擎基板级别规则</t>
-        </is>
-      </c>
-      <c r="W113" t="inlineStr"/>
+          <t>特殊需求及引擎基板级别规则；业务确认：1oz以下不包含1oz</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -11298,7 +10731,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -11336,11 +10769,6 @@
           <t>铜厚:1oz</t>
         </is>
       </c>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
       <c r="O114" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -11376,8 +10804,11 @@
           <t>118</t>
         </is>
       </c>
-      <c r="V114" t="inlineStr"/>
-      <c r="W114" t="inlineStr"/>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>停用拆分错误的1oz宽泛规则；由NY2140+厚度&gt;=0.8+铜厚&lt;1oz完整规则执行</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -11417,12 +10848,12 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=F1 | 条件=胶系:NY2140；厚度&gt;=0.8；铜厚&lt;=1oz | 状态=可执行草稿 | 依据=特殊需求及引擎基板级别规则</t>
+          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=F1 | 条件=胶系:NY2140；厚度&gt;=0.8；铜厚&lt;1oz | 状态=可执行草稿 | 依据=特殊需求及引擎基板级别规则</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>胶系:NY2140；厚度&gt;=0.8；铜厚&lt;=1oz</t>
+          <t>胶系:NY2140；厚度&gt;=0.8；铜厚&lt;1oz</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -11430,14 +10861,16 @@
           <t>NY2140</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>&lt;1oz</t>
+        </is>
+      </c>
       <c r="M115" t="inlineStr">
         <is>
           <t>&gt;=0.8</t>
         </is>
       </c>
-      <c r="N115" t="inlineStr"/>
       <c r="O115" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -11475,10 +10908,9 @@
       </c>
       <c r="V115" t="inlineStr">
         <is>
-          <t>特殊需求及引擎基板级别规则</t>
-        </is>
-      </c>
-      <c r="W115" t="inlineStr"/>
+          <t>特殊需求及引擎基板级别规则；业务确认：1oz以下不包含1oz</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -11536,9 +10968,6 @@
           <t>NY3150HF</t>
         </is>
       </c>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
       <c r="O116" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -11574,8 +11003,6 @@
           <t>120</t>
         </is>
       </c>
-      <c r="V116" t="inlineStr"/>
-      <c r="W116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -11615,7 +11042,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=AH AD | 条件=胶系:NY3150HF；关键词:NY3150HF | 状态=可执行草稿</t>
+          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=AD | 条件=胶系:NY3150HF；关键词:NY3150HF | 状态=可执行草稿</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -11633,9 +11060,6 @@
           <t>NY3150HF</t>
         </is>
       </c>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -11643,7 +11067,7 @@
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>AH</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="Q117" t="inlineStr">
@@ -11671,8 +11095,11 @@
           <t>121</t>
         </is>
       </c>
-      <c r="V117" t="inlineStr"/>
-      <c r="W117" t="inlineStr"/>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>原文AH为客户胶系代码，AD为基板级别代码</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -11730,9 +11157,6 @@
           <t>NY-A2</t>
         </is>
       </c>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -11768,8 +11192,6 @@
           <t>132</t>
         </is>
       </c>
-      <c r="V118" t="inlineStr"/>
-      <c r="W118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -11817,15 +11239,11 @@
           <t>厚度&gt;=0.8</t>
         </is>
       </c>
-      <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr">
         <is>
           <t>&gt;=0.8</t>
         </is>
       </c>
-      <c r="N119" t="inlineStr"/>
       <c r="O119" t="inlineStr">
         <is>
           <t>tc_code</t>
@@ -11866,7 +11284,6 @@
           <t>由原始CCL总/芯厚阈值重建，避免结构化列把&gt;=与&lt;条件拆丢</t>
         </is>
       </c>
-      <c r="W119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -11914,15 +11331,11 @@
           <t>厚度&lt;0.8</t>
         </is>
       </c>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr">
         <is>
           <t>&lt;0.8</t>
         </is>
       </c>
-      <c r="N120" t="inlineStr"/>
       <c r="O120" t="inlineStr">
         <is>
           <t>tc_code</t>
@@ -11963,7 +11376,6 @@
           <t>由原始CCL总/芯厚阈值重建，避免结构化列把&gt;=与&lt;条件拆丢</t>
         </is>
       </c>
-      <c r="W120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -12011,15 +11423,11 @@
           <t>厚度&gt;=0.8</t>
         </is>
       </c>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr">
         <is>
           <t>&gt;=0.8</t>
         </is>
       </c>
-      <c r="N121" t="inlineStr"/>
       <c r="O121" t="inlineStr">
         <is>
           <t>tc_code</t>
@@ -12060,7 +11468,6 @@
           <t>由原始CCL总/芯厚阈值重建，避免结构化列把&gt;=与&lt;条件拆丢</t>
         </is>
       </c>
-      <c r="W121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -12108,15 +11515,11 @@
           <t>厚度&lt;0.8</t>
         </is>
       </c>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
       <c r="M122" t="inlineStr">
         <is>
           <t>&lt;0.8</t>
         </is>
       </c>
-      <c r="N122" t="inlineStr"/>
       <c r="O122" t="inlineStr">
         <is>
           <t>tc_code</t>
@@ -12157,7 +11560,6 @@
           <t>由原始CCL总/芯厚阈值重建，避免结构化列把&gt;=与&lt;条件拆丢</t>
         </is>
       </c>
-      <c r="W122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -12205,15 +11607,11 @@
           <t>厚度&gt;=0.8</t>
         </is>
       </c>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr">
         <is>
           <t>&gt;=0.8</t>
         </is>
       </c>
-      <c r="N123" t="inlineStr"/>
       <c r="O123" t="inlineStr">
         <is>
           <t>tc_code</t>
@@ -12254,7 +11652,6 @@
           <t>由原始CCL总/芯厚阈值重建，避免结构化列把&gt;=与&lt;条件拆丢</t>
         </is>
       </c>
-      <c r="W123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -12302,15 +11699,11 @@
           <t>厚度&lt;0.8</t>
         </is>
       </c>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr">
         <is>
           <t>&lt;0.8</t>
         </is>
       </c>
-      <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr">
         <is>
           <t>tc_code</t>
@@ -12351,7 +11744,6 @@
           <t>由原始CCL总/芯厚阈值重建，避免结构化列把&gt;=与&lt;条件拆丢</t>
         </is>
       </c>
-      <c r="W124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -12399,15 +11791,11 @@
           <t>关键词:HS2-M2-VSP</t>
         </is>
       </c>
-      <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr">
         <is>
           <t>HS2-M2-VSP</t>
         </is>
       </c>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
       <c r="O125" t="inlineStr">
         <is>
           <t>copper_type_code</t>
@@ -12443,8 +11831,6 @@
           <t>137</t>
         </is>
       </c>
-      <c r="V125" t="inlineStr"/>
-      <c r="W125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -12492,15 +11878,11 @@
           <t>关键词:HS1-M2-VSP</t>
         </is>
       </c>
-      <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
           <t>HS1-M2-VSP</t>
         </is>
       </c>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
       <c r="O126" t="inlineStr">
         <is>
           <t>copper_type_code</t>
@@ -12536,8 +11918,6 @@
           <t>137</t>
         </is>
       </c>
-      <c r="V126" t="inlineStr"/>
-      <c r="W126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -12585,15 +11965,11 @@
           <t>关键词:HS2-M2-VSP</t>
         </is>
       </c>
-      <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
           <t>HS2-M2-VSP</t>
         </is>
       </c>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
       <c r="O127" t="inlineStr">
         <is>
           <t>copper_type_code</t>
@@ -12629,8 +12005,6 @@
           <t>138</t>
         </is>
       </c>
-      <c r="V127" t="inlineStr"/>
-      <c r="W127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -12678,15 +12052,11 @@
           <t>关键词:HS1-M2-VSP</t>
         </is>
       </c>
-      <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
           <t>HS1-M2-VSP</t>
         </is>
       </c>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
       <c r="O128" t="inlineStr">
         <is>
           <t>copper_type_code</t>
@@ -12722,8 +12092,6 @@
           <t>138</t>
         </is>
       </c>
-      <c r="V128" t="inlineStr"/>
-      <c r="W128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -12771,15 +12139,11 @@
           <t>关键词:HS2-M2-VSP</t>
         </is>
       </c>
-      <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr">
         <is>
           <t>HS2-M2-VSP</t>
         </is>
       </c>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
       <c r="O129" t="inlineStr">
         <is>
           <t>copper_type_code</t>
@@ -12815,8 +12179,6 @@
           <t>139</t>
         </is>
       </c>
-      <c r="V129" t="inlineStr"/>
-      <c r="W129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -12864,15 +12226,11 @@
           <t>关键词:HS1-M2-VSP</t>
         </is>
       </c>
-      <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
           <t>HS1-M2-VSP</t>
         </is>
       </c>
-      <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
       <c r="O130" t="inlineStr">
         <is>
           <t>copper_type_code</t>
@@ -12908,8 +12266,6 @@
           <t>139</t>
         </is>
       </c>
-      <c r="V130" t="inlineStr"/>
-      <c r="W130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -12957,15 +12313,11 @@
           <t>胶系:NY2140；关键词:TG140</t>
         </is>
       </c>
-      <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr">
         <is>
           <t>TG140</t>
         </is>
       </c>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
       <c r="O131" t="inlineStr">
         <is>
           <t>glue_code</t>
@@ -13001,8 +12353,6 @@
           <t>144</t>
         </is>
       </c>
-      <c r="V131" t="inlineStr"/>
-      <c r="W131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -13050,15 +12400,11 @@
           <t>胶系:NY2150；关键词:TG150</t>
         </is>
       </c>
-      <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
           <t>TG150</t>
         </is>
       </c>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
       <c r="O132" t="inlineStr">
         <is>
           <t>glue_code</t>
@@ -13094,8 +12440,6 @@
           <t>144</t>
         </is>
       </c>
-      <c r="V132" t="inlineStr"/>
-      <c r="W132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -13143,15 +12487,11 @@
           <t>胶系:NY2170；关键词:TG170</t>
         </is>
       </c>
-      <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
           <t>TG170</t>
         </is>
       </c>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
       <c r="O133" t="inlineStr">
         <is>
           <t>glue_code</t>
@@ -13187,8 +12527,6 @@
           <t>144</t>
         </is>
       </c>
-      <c r="V133" t="inlineStr"/>
-      <c r="W133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -13236,7 +12574,6 @@
           <t>关键词:客户W/W</t>
         </is>
       </c>
-      <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
           <t>客户W/W</t>
@@ -13247,8 +12584,6 @@
           <t>W/W</t>
         </is>
       </c>
-      <c r="M134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
       <c r="O134" t="inlineStr">
         <is>
           <t>copper_code</t>
@@ -13284,8 +12619,6 @@
           <t>144</t>
         </is>
       </c>
-      <c r="V134" t="inlineStr"/>
-      <c r="W134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -13333,15 +12666,11 @@
           <t>关键词:PVLP</t>
         </is>
       </c>
-      <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
           <t>PVLP</t>
         </is>
       </c>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
       <c r="O135" t="inlineStr">
         <is>
           <t>copper_type_code</t>
@@ -13377,8 +12706,6 @@
           <t>145</t>
         </is>
       </c>
-      <c r="V135" t="inlineStr"/>
-      <c r="W135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -13426,15 +12753,11 @@
           <t>关键词:FVLP</t>
         </is>
       </c>
-      <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr">
         <is>
           <t>FVLP</t>
         </is>
       </c>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
       <c r="O136" t="inlineStr">
         <is>
           <t>copper_type_code</t>
@@ -13470,8 +12793,6 @@
           <t>145</t>
         </is>
       </c>
-      <c r="V136" t="inlineStr"/>
-      <c r="W136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -13519,15 +12840,11 @@
           <t>关键词:HVLP</t>
         </is>
       </c>
-      <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr">
         <is>
           <t>HVLP</t>
         </is>
       </c>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr">
         <is>
           <t>copper_type_code</t>
@@ -13563,8 +12880,6 @@
           <t>145</t>
         </is>
       </c>
-      <c r="V137" t="inlineStr"/>
-      <c r="W137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -13612,15 +12927,11 @@
           <t>关键词:PVLP</t>
         </is>
       </c>
-      <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr">
         <is>
           <t>PVLP</t>
         </is>
       </c>
-      <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
       <c r="O138" t="inlineStr">
         <is>
           <t>copper_type_code</t>
@@ -13656,8 +12967,6 @@
           <t>146</t>
         </is>
       </c>
-      <c r="V138" t="inlineStr"/>
-      <c r="W138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -13705,15 +13014,11 @@
           <t>关键词:FVLP</t>
         </is>
       </c>
-      <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr">
         <is>
           <t>FVLP</t>
         </is>
       </c>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
       <c r="O139" t="inlineStr">
         <is>
           <t>copper_type_code</t>
@@ -13749,8 +13054,6 @@
           <t>146</t>
         </is>
       </c>
-      <c r="V139" t="inlineStr"/>
-      <c r="W139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -13798,15 +13101,11 @@
           <t>关键词:HVLP</t>
         </is>
       </c>
-      <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr">
         <is>
           <t>HVLP</t>
         </is>
       </c>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
       <c r="O140" t="inlineStr">
         <is>
           <t>copper_type_code</t>
@@ -13842,8 +13141,6 @@
           <t>146</t>
         </is>
       </c>
-      <c r="V140" t="inlineStr"/>
-      <c r="W140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -13901,9 +13198,6 @@
           <t>NY2140</t>
         </is>
       </c>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
       <c r="O141" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -13939,8 +13233,6 @@
           <t>156</t>
         </is>
       </c>
-      <c r="V141" t="inlineStr"/>
-      <c r="W141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -13998,9 +13290,6 @@
           <t>NY2140L</t>
         </is>
       </c>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr"/>
-      <c r="N142" t="inlineStr"/>
       <c r="O142" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -14036,8 +13325,6 @@
           <t>156</t>
         </is>
       </c>
-      <c r="V142" t="inlineStr"/>
-      <c r="W142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -14077,27 +13364,24 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=AC | 条件=厚度:9；关键词:9mm（含）以下 | 状态=可执行草稿</t>
+          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=A1 | 条件=胶系:NY2150/NY2170；厚度:&gt;0.9 | 状态=可执行草稿</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>厚度:9；关键词:9mm（含）以下</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>9mm（含）以下</t>
-        </is>
-      </c>
-      <c r="L143" t="inlineStr"/>
+          <t>胶系:NY2150/NY2170；厚度:&gt;0.9</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>NY2150/NY2170</t>
+        </is>
+      </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="N143" t="inlineStr"/>
+          <t>&gt;0.9</t>
+        </is>
+      </c>
       <c r="O143" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -14105,7 +13389,7 @@
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="Q143" t="inlineStr">
@@ -14115,7 +13399,7 @@
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="S143" t="inlineStr">
@@ -14133,8 +13417,6 @@
           <t>156</t>
         </is>
       </c>
-      <c r="V143" t="inlineStr"/>
-      <c r="W143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -14164,37 +13446,34 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>规则来源说明</t>
+          <t>CCL特殊规则</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>业务反馈复核</t>
+          <t>基板级别</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>复核说明：业务反馈确认“0.9mm以下”不含0.9；边界清楚：NY2150/NY2170厚度&gt;=0.9mm为A1，厚度&lt;0.9mm为AC。</t>
+          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=AC | 条件=胶系:NY2150/NY2170；厚度:&lt;=0.9 | 状态=可执行草稿</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>胶系:NY2150；厚度:&gt;=0.9</t>
+          <t>胶系:NY2150/NY2170；厚度:&lt;=0.9</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>NY2150</t>
-        </is>
-      </c>
-      <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr"/>
+          <t>NY2150/NY2170</t>
+        </is>
+      </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>&gt;=0.9</t>
-        </is>
-      </c>
-      <c r="N144" t="inlineStr"/>
+          <t>&lt;=0.9</t>
+        </is>
+      </c>
       <c r="O144" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -14202,17 +13481,17 @@
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>客户特殊规则确认草稿/业务反馈复核</t>
+          <t>客户特殊规则确认草稿</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>1160</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="S144" t="inlineStr">
@@ -14230,12 +13509,6 @@
           <t>156</t>
         </is>
       </c>
-      <c r="V144" t="inlineStr">
-        <is>
-          <t>由业务反馈复核行补充生成</t>
-        </is>
-      </c>
-      <c r="W144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -14275,12 +13548,12 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>复核说明：业务反馈确认“0.9mm以下”不含0.9；边界清楚：NY2150/NY2170厚度&gt;=0.9mm为A1，厚度&lt;0.9mm为AC。</t>
+          <t>复核说明：NY2150/NY2170厚度&lt;=0.9mm为AC，厚度&gt;0.9mm为A1。</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>胶系:NY2150；厚度:&lt;0.9</t>
+          <t>胶系:NY2150；厚度:&lt;=0.9</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -14288,14 +13561,11 @@
           <t>NY2150</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr"/>
       <c r="M145" t="inlineStr">
         <is>
-          <t>&lt;0.9</t>
-        </is>
-      </c>
-      <c r="N145" t="inlineStr"/>
+          <t>&lt;=0.9</t>
+        </is>
+      </c>
       <c r="O145" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -14336,7 +13606,6 @@
           <t>由业务反馈复核行补充生成</t>
         </is>
       </c>
-      <c r="W145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -14376,27 +13645,24 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>复核说明：业务反馈确认“0.9mm以下”不含0.9；边界清楚：NY2150/NY2170厚度&gt;=0.9mm为A1，厚度&lt;0.9mm为AC。</t>
+          <t>复核说明：NY2150/NY2170厚度&lt;=0.9mm为AC，厚度&gt;0.9mm为A1。</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>胶系:NY2170；厚度:&gt;=0.9</t>
+          <t>胶系:NY2150；厚度:&gt;0.9</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>NY2170</t>
-        </is>
-      </c>
-      <c r="K146" t="inlineStr"/>
-      <c r="L146" t="inlineStr"/>
+          <t>NY2150</t>
+        </is>
+      </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>&gt;=0.9</t>
-        </is>
-      </c>
-      <c r="N146" t="inlineStr"/>
+          <t>&gt;0.9</t>
+        </is>
+      </c>
       <c r="O146" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -14437,7 +13703,6 @@
           <t>由业务反馈复核行补充生成</t>
         </is>
       </c>
-      <c r="W146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -14477,12 +13742,12 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>复核说明：业务反馈确认“0.9mm以下”不含0.9；边界清楚：NY2150/NY2170厚度&gt;=0.9mm为A1，厚度&lt;0.9mm为AC。</t>
+          <t>复核说明：NY2150/NY2170厚度&lt;=0.9mm为AC，厚度&gt;0.9mm为A1。</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>胶系:NY2170；厚度:&lt;0.9</t>
+          <t>胶系:NY2170；厚度:&lt;=0.9</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -14490,14 +13755,11 @@
           <t>NY2170</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
-      <c r="L147" t="inlineStr"/>
       <c r="M147" t="inlineStr">
         <is>
-          <t>&lt;0.9</t>
-        </is>
-      </c>
-      <c r="N147" t="inlineStr"/>
+          <t>&lt;=0.9</t>
+        </is>
+      </c>
       <c r="O147" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -14538,7 +13800,6 @@
           <t>由业务反馈复核行补充生成</t>
         </is>
       </c>
-      <c r="W147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -14553,12 +13814,12 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>123004</t>
+          <t>106011</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>信丰共赢</t>
+          <t>川华兴宇</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -14568,33 +13829,34 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>CCL特殊规则</t>
+          <t>规则来源说明</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>基板级别</t>
+          <t>业务反馈复核</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=F1料号 | 条件=铜厚:1oz；关键词:8(含)以上&amp;1oz铜箔以下 | 状态=可执行草稿</t>
+          <t>复核说明：NY2150/NY2170厚度&lt;=0.9mm为AC，厚度&gt;0.9mm为A1。</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>铜厚:1oz；关键词:8(含)以上&amp;1oz铜箔以下</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr"/>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t>8(含)以上&amp;1oz铜箔以下</t>
-        </is>
-      </c>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr"/>
-      <c r="N148" t="inlineStr"/>
+          <t>胶系:NY2170；厚度:&gt;0.9</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>NY2170</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>&gt;0.9</t>
+        </is>
+      </c>
       <c r="O148" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -14602,17 +13864,17 @@
       </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>客户特殊规则确认草稿</t>
+          <t>客户特殊规则确认草稿/业务反馈复核</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1160</t>
         </is>
       </c>
       <c r="S148" t="inlineStr">
@@ -14627,11 +13889,14 @@
       </c>
       <c r="U148" t="inlineStr">
         <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="V148" t="inlineStr"/>
-      <c r="W148" t="inlineStr"/>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>由业务反馈复核行补充生成</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -14641,7 +13906,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -14671,27 +13936,19 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=F1 | 条件=胶系:NY2140；厚度&gt;=0.8；铜厚&lt;=1oz | 状态=可执行草稿 | 依据=特殊需求及引擎基板级别规则</t>
+          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=F1料号 | 条件=铜厚:1oz；关键词:8(含)以上&amp;1oz铜箔以下 | 状态=可执行草稿</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>胶系:NY2140；厚度&gt;=0.8；铜厚&lt;=1oz</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>NY2140</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>&gt;=0.8</t>
-        </is>
-      </c>
-      <c r="N149" t="inlineStr"/>
+          <t>铜厚:1oz；关键词:8(含)以上&amp;1oz铜箔以下</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>8(含)以上&amp;1oz铜箔以下</t>
+        </is>
+      </c>
       <c r="O149" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -14709,7 +13966,7 @@
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="S149" t="inlineStr">
@@ -14727,12 +13984,11 @@
           <t>169</t>
         </is>
       </c>
-      <c r="V149" t="inlineStr">
-        <is>
-          <t>特殊需求及引擎基板级别规则</t>
-        </is>
-      </c>
-      <c r="W149" t="inlineStr"/>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>停用拆分错误的1oz宽泛规则；由NY2140+厚度&gt;=0.8+铜厚&lt;1oz完整规则执行</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -14762,7 +14018,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>通用特殊规则</t>
+          <t>CCL特殊规则</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -14772,12 +14028,12 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=F1 | 条件=胶系:NY2140；厚度&gt;=0.8；铜厚&lt;=1oz | 状态=可执行草稿 | 依据=通用特殊规则及引擎基板级别规则</t>
+          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=F1 | 条件=胶系:NY2140；厚度&gt;=0.8；铜厚&lt;1oz | 状态=可执行草稿 | 依据=特殊需求及引擎基板级别规则</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>胶系:NY2140；厚度&gt;=0.8；铜厚&lt;=1oz</t>
+          <t>胶系:NY2140；厚度&gt;=0.8；铜厚&lt;1oz</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -14785,14 +14041,16 @@
           <t>NY2140</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>&lt;1oz</t>
+        </is>
+      </c>
       <c r="M150" t="inlineStr">
         <is>
           <t>&gt;=0.8</t>
         </is>
       </c>
-      <c r="N150" t="inlineStr"/>
       <c r="O150" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -14810,7 +14068,7 @@
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="S150" t="inlineStr">
@@ -14830,10 +14088,9 @@
       </c>
       <c r="V150" t="inlineStr">
         <is>
-          <t>通用特殊规则及引擎基板级别规则</t>
-        </is>
-      </c>
-      <c r="W150" t="inlineStr"/>
+          <t>特殊需求及引擎基板级别规则；业务确认：1oz以下不包含1oz</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -14848,12 +14105,12 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>123021</t>
+          <t>123004</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>信迅捷兴</t>
+          <t>信丰共赢</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -14863,7 +14120,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>CCL特殊规则</t>
+          <t>通用特殊规则</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -14873,23 +14130,29 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=F1料号 | 条件=铜厚:1oz；关键词:8(含)以上&amp;1oz铜箔以下 | 状态=可执行草稿</t>
+          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=F1 | 条件=胶系:NY2140；厚度&gt;=0.8；铜厚&lt;1oz | 状态=可执行草稿 | 依据=通用特殊规则及引擎基板级别规则</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>铜厚:1oz；关键词:8(含)以上&amp;1oz铜箔以下</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr"/>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>8(含)以上&amp;1oz铜箔以下</t>
-        </is>
-      </c>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr"/>
-      <c r="N151" t="inlineStr"/>
+          <t>胶系:NY2140；厚度&gt;=0.8；铜厚&lt;1oz</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>NY2140</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>&lt;1oz</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>&gt;=0.8</t>
+        </is>
+      </c>
       <c r="O151" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -14907,7 +14170,7 @@
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>950</t>
         </is>
       </c>
       <c r="S151" t="inlineStr">
@@ -14922,11 +14185,14 @@
       </c>
       <c r="U151" t="inlineStr">
         <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="V151" t="inlineStr"/>
-      <c r="W151" t="inlineStr"/>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>通用特殊规则及引擎基板级别规则；业务确认：1oz以下不包含1oz</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -14936,7 +14202,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -14966,27 +14232,19 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=F1 | 条件=胶系:NY2140；厚度&gt;=0.8；铜厚&lt;=1oz | 状态=可执行草稿 | 依据=特殊需求及引擎基板级别规则</t>
+          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=F1料号 | 条件=铜厚:1oz；关键词:8(含)以上&amp;1oz铜箔以下 | 状态=可执行草稿</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>胶系:NY2140；厚度&gt;=0.8；铜厚&lt;=1oz</t>
-        </is>
-      </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>NY2140</t>
-        </is>
-      </c>
-      <c r="K152" t="inlineStr"/>
-      <c r="L152" t="inlineStr"/>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>&gt;=0.8</t>
-        </is>
-      </c>
-      <c r="N152" t="inlineStr"/>
+          <t>铜厚:1oz；关键词:8(含)以上&amp;1oz铜箔以下</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>8(含)以上&amp;1oz铜箔以下</t>
+        </is>
+      </c>
       <c r="O152" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -15004,7 +14262,7 @@
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="S152" t="inlineStr">
@@ -15022,12 +14280,11 @@
           <t>170</t>
         </is>
       </c>
-      <c r="V152" t="inlineStr">
-        <is>
-          <t>特殊需求及引擎基板级别规则</t>
-        </is>
-      </c>
-      <c r="W152" t="inlineStr"/>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>停用拆分错误的1oz宽泛规则；由NY2140+厚度&gt;=0.8+铜厚&lt;1oz完整规则执行</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -15042,12 +14299,12 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>103006</t>
+          <t>123021</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>中宝悦嘉</t>
+          <t>信迅捷兴</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -15062,36 +14319,42 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>铜箔规格</t>
+          <t>基板级别</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>字段=铜箔规格 | 目标=铜箔规格代码 | 覆盖字段=copper_code | 覆盖值=JJ | 条件=关键词:H-/H- | 状态=可执行草稿</t>
+          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=F1 | 条件=胶系:NY2140；厚度&gt;=0.8；铜厚&lt;1oz | 状态=可执行草稿 | 依据=特殊需求及引擎基板级别规则</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>关键词:H-/H-</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr"/>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>H-/H-</t>
-        </is>
-      </c>
-      <c r="L153" t="inlineStr"/>
-      <c r="M153" t="inlineStr"/>
-      <c r="N153" t="inlineStr"/>
+          <t>胶系:NY2140；厚度&gt;=0.8；铜厚&lt;1oz</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>NY2140</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>&lt;1oz</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>&gt;=0.8</t>
+        </is>
+      </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>copper_code</t>
+          <t>grade_code</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>JJ</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="Q153" t="inlineStr">
@@ -15101,7 +14364,7 @@
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="S153" t="inlineStr">
@@ -15116,11 +14379,14 @@
       </c>
       <c r="U153" t="inlineStr">
         <is>
-          <t>171</t>
-        </is>
-      </c>
-      <c r="V153" t="inlineStr"/>
-      <c r="W153" t="inlineStr"/>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>特殊需求及引擎基板级别规则；业务确认：1oz以下不包含1oz</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -15155,32 +14421,32 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>基板级别</t>
+          <t>铜箔规格</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=F1 | 条件=铜厚:1oz | 状态=可执行草稿</t>
+          <t>字段=铜箔规格 | 目标=铜箔规格代码 | 覆盖字段=copper_code | 覆盖值=JJ | 条件=关键词:H-/H- | 状态=可执行草稿</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>铜厚:1oz</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr"/>
-      <c r="K154" t="inlineStr"/>
-      <c r="L154" t="inlineStr"/>
-      <c r="M154" t="inlineStr"/>
-      <c r="N154" t="inlineStr"/>
+          <t>关键词:H-/H-</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>H-/H-</t>
+        </is>
+      </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>grade_code</t>
+          <t>copper_code</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>JJ</t>
         </is>
       </c>
       <c r="Q154" t="inlineStr">
@@ -15190,7 +14456,7 @@
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="S154" t="inlineStr">
@@ -15208,8 +14474,6 @@
           <t>171</t>
         </is>
       </c>
-      <c r="V154" t="inlineStr"/>
-      <c r="W154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -15219,7 +14483,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -15249,27 +14513,14 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=A2 | 条件=胶系:NY1600；关键词:NY1600 | 状态=可执行草稿</t>
+          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=F1 | 条件=铜厚:1oz | 状态=可执行草稿</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>胶系:NY1600；关键词:NY1600</t>
-        </is>
-      </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>NY1600</t>
-        </is>
-      </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t>NY1600</t>
-        </is>
-      </c>
-      <c r="L155" t="inlineStr"/>
-      <c r="M155" t="inlineStr"/>
-      <c r="N155" t="inlineStr"/>
+          <t>铜厚:1oz</t>
+        </is>
+      </c>
       <c r="O155" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -15277,7 +14528,7 @@
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="Q155" t="inlineStr">
@@ -15287,7 +14538,7 @@
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="S155" t="inlineStr">
@@ -15305,8 +14556,11 @@
           <t>171</t>
         </is>
       </c>
-      <c r="V155" t="inlineStr"/>
-      <c r="W155" t="inlineStr"/>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>停用拆分错误的1oz宽泛规则；由NY2140+厚度&gt;=0.8+铜厚&lt;1oz完整规则执行</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -15346,27 +14600,24 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=F1 | 条件=胶系:NY2140；厚度&gt;=0.8；铜厚&lt;=1oz | 状态=可执行草稿 | 依据=特殊需求及引擎基板级别规则</t>
+          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=A2 | 条件=胶系:NY1600；关键词:NY1600 | 状态=可执行草稿</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>胶系:NY2140；厚度&gt;=0.8；铜厚&lt;=1oz</t>
+          <t>胶系:NY1600；关键词:NY1600</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>NY2140</t>
-        </is>
-      </c>
-      <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr"/>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>&gt;=0.8</t>
-        </is>
-      </c>
-      <c r="N156" t="inlineStr"/>
+          <t>NY1600</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>NY1600</t>
+        </is>
+      </c>
       <c r="O156" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -15374,7 +14625,7 @@
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="Q156" t="inlineStr">
@@ -15402,12 +14653,6 @@
           <t>171</t>
         </is>
       </c>
-      <c r="V156" t="inlineStr">
-        <is>
-          <t>特殊需求及引擎基板级别规则</t>
-        </is>
-      </c>
-      <c r="W156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -15422,12 +14667,12 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>123008</t>
+          <t>103006</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>九江明阳</t>
+          <t>中宝悦嘉</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -15442,40 +14687,42 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>铜箔规格</t>
+          <t>基板级别</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>字段=铜箔规格 | 目标=铜箔规格代码 | 覆盖字段=copper_code | 覆盖值=FF | 条件=关键词:W/W | 状态=可执行草稿</t>
+          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=F1 | 条件=胶系:NY2140；厚度&gt;=0.8；铜厚&lt;1oz | 状态=可执行草稿 | 依据=特殊需求及引擎基板级别规则</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>关键词:W/W</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr"/>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t>W/W</t>
+          <t>胶系:NY2140；厚度&gt;=0.8；铜厚&lt;1oz</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>NY2140</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>W/W</t>
-        </is>
-      </c>
-      <c r="M157" t="inlineStr"/>
-      <c r="N157" t="inlineStr"/>
+          <t>&lt;1oz</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>&gt;=0.8</t>
+        </is>
+      </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>copper_code</t>
+          <t>grade_code</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>FF</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="Q157" t="inlineStr">
@@ -15485,7 +14732,7 @@
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="S157" t="inlineStr">
@@ -15500,11 +14747,14 @@
       </c>
       <c r="U157" t="inlineStr">
         <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="V157" t="inlineStr"/>
-      <c r="W157" t="inlineStr"/>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>特殊需求及引擎基板级别规则；业务确认：1oz以下不包含1oz</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -15539,32 +14789,37 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>基板级别</t>
+          <t>铜箔规格</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=F1 | 条件=铜厚:1oz | 状态=可执行草稿</t>
+          <t>字段=铜箔规格 | 目标=铜箔规格代码 | 覆盖字段=copper_code | 覆盖值=FF | 条件=关键词:W/W | 状态=可执行草稿</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>铜厚:1oz</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr"/>
-      <c r="K158" t="inlineStr"/>
-      <c r="L158" t="inlineStr"/>
-      <c r="M158" t="inlineStr"/>
-      <c r="N158" t="inlineStr"/>
+          <t>关键词:W/W</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>W/W</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>W/W</t>
+        </is>
+      </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>grade_code</t>
+          <t>copper_code</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>FF</t>
         </is>
       </c>
       <c r="Q158" t="inlineStr">
@@ -15574,7 +14829,7 @@
       </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="S158" t="inlineStr">
@@ -15592,8 +14847,6 @@
           <t>174</t>
         </is>
       </c>
-      <c r="V158" t="inlineStr"/>
-      <c r="W158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -15603,7 +14856,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -15633,27 +14886,14 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=F1 | 条件=胶系:NY2140；厚度&gt;=0.8；铜厚&lt;=1oz | 状态=可执行草稿 | 依据=特殊需求及引擎基板级别规则</t>
+          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=F1 | 条件=铜厚:1oz | 状态=可执行草稿</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>胶系:NY2140；厚度&gt;=0.8；铜厚&lt;=1oz</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>NY2140</t>
-        </is>
-      </c>
-      <c r="K159" t="inlineStr"/>
-      <c r="L159" t="inlineStr"/>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>&gt;=0.8</t>
-        </is>
-      </c>
-      <c r="N159" t="inlineStr"/>
+          <t>铜厚:1oz</t>
+        </is>
+      </c>
       <c r="O159" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -15671,7 +14911,7 @@
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="S159" t="inlineStr">
@@ -15689,12 +14929,11 @@
           <t>174</t>
         </is>
       </c>
-      <c r="V159" t="inlineStr">
-        <is>
-          <t>特殊需求及引擎基板级别规则</t>
-        </is>
-      </c>
-      <c r="W159" t="inlineStr"/>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>停用拆分错误的1oz宽泛规则；由NY2140+厚度&gt;=0.8+铜厚&lt;1oz完整规则执行</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -15709,12 +14948,12 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>103045</t>
+          <t>123008</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>深圳明阳</t>
+          <t>九江明阳</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -15729,40 +14968,42 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>铜箔规格</t>
+          <t>基板级别</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>字段=铜箔规格 | 目标=铜箔规格代码 | 覆盖字段=copper_code | 覆盖值=FF | 条件=关键词:W/W | 状态=可执行草稿</t>
+          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=F1 | 条件=胶系:NY2140；厚度&gt;=0.8；铜厚&lt;1oz | 状态=可执行草稿 | 依据=特殊需求及引擎基板级别规则</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>关键词:W/W</t>
-        </is>
-      </c>
-      <c r="J160" t="inlineStr"/>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>W/W</t>
+          <t>胶系:NY2140；厚度&gt;=0.8；铜厚&lt;1oz</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>NY2140</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>W/W</t>
-        </is>
-      </c>
-      <c r="M160" t="inlineStr"/>
-      <c r="N160" t="inlineStr"/>
+          <t>&lt;1oz</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>&gt;=0.8</t>
+        </is>
+      </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>copper_code</t>
+          <t>grade_code</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>FF</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="Q160" t="inlineStr">
@@ -15772,7 +15013,7 @@
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="S160" t="inlineStr">
@@ -15787,11 +15028,14 @@
       </c>
       <c r="U160" t="inlineStr">
         <is>
-          <t>175</t>
-        </is>
-      </c>
-      <c r="V160" t="inlineStr"/>
-      <c r="W160" t="inlineStr"/>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>特殊需求及引擎基板级别规则；业务确认：1oz以下不包含1oz</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -15826,32 +15070,37 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>基板级别</t>
+          <t>铜箔规格</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=F1 | 条件=铜厚:1oz | 状态=可执行草稿</t>
+          <t>字段=铜箔规格 | 目标=铜箔规格代码 | 覆盖字段=copper_code | 覆盖值=FF | 条件=关键词:W/W | 状态=可执行草稿</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>铜厚:1oz</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr"/>
-      <c r="K161" t="inlineStr"/>
-      <c r="L161" t="inlineStr"/>
-      <c r="M161" t="inlineStr"/>
-      <c r="N161" t="inlineStr"/>
+          <t>关键词:W/W</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>W/W</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>W/W</t>
+        </is>
+      </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>grade_code</t>
+          <t>copper_code</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>FF</t>
         </is>
       </c>
       <c r="Q161" t="inlineStr">
@@ -15861,7 +15110,7 @@
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="S161" t="inlineStr">
@@ -15879,8 +15128,6 @@
           <t>175</t>
         </is>
       </c>
-      <c r="V161" t="inlineStr"/>
-      <c r="W161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -15890,7 +15137,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -15920,27 +15167,14 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=F1 | 条件=胶系:NY2140；厚度&gt;=0.8；铜厚&lt;=1oz | 状态=可执行草稿 | 依据=特殊需求及引擎基板级别规则</t>
+          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=F1 | 条件=铜厚:1oz | 状态=可执行草稿</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>胶系:NY2140；厚度&gt;=0.8；铜厚&lt;=1oz</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>NY2140</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr"/>
-      <c r="L162" t="inlineStr"/>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>&gt;=0.8</t>
-        </is>
-      </c>
-      <c r="N162" t="inlineStr"/>
+          <t>铜厚:1oz</t>
+        </is>
+      </c>
       <c r="O162" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -15958,7 +15192,7 @@
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="S162" t="inlineStr">
@@ -15976,12 +15210,11 @@
           <t>175</t>
         </is>
       </c>
-      <c r="V162" t="inlineStr">
-        <is>
-          <t>特殊需求及引擎基板级别规则</t>
-        </is>
-      </c>
-      <c r="W162" t="inlineStr"/>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>停用拆分错误的1oz宽泛规则；由NY2140+厚度&gt;=0.8+铜厚&lt;1oz完整规则执行</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -15996,12 +15229,12 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>105011</t>
+          <t>103045</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>湖南鹰飞</t>
+          <t>深圳明阳</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -16016,40 +15249,42 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>胶系</t>
+          <t>基板级别</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>字段=胶系 | 目标=胶系代码 | 覆盖字段=glue_code | 覆盖值=2A | 条件=厚度:2；关键词:普通板 | 状态=可执行草稿</t>
+          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=F1 | 条件=胶系:NY2140；厚度&gt;=0.8；铜厚&lt;1oz | 状态=可执行草稿 | 依据=特殊需求及引擎基板级别规则</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>厚度:2；关键词:普通板</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr"/>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t>普通板</t>
-        </is>
-      </c>
-      <c r="L163" t="inlineStr"/>
+          <t>胶系:NY2140；厚度&gt;=0.8；铜厚&lt;1oz</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>NY2140</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>&lt;1oz</t>
+        </is>
+      </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N163" t="inlineStr"/>
+          <t>&gt;=0.8</t>
+        </is>
+      </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>glue_code</t>
+          <t>grade_code</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>2A</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="Q163" t="inlineStr">
@@ -16059,7 +15294,7 @@
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="S163" t="inlineStr">
@@ -16074,11 +15309,14 @@
       </c>
       <c r="U163" t="inlineStr">
         <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="V163" t="inlineStr"/>
-      <c r="W163" t="inlineStr"/>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>特殊需求及引擎基板级别规则；业务确认：1oz以下不包含1oz</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -16118,23 +15356,24 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>字段=胶系 | 目标=胶系代码 | 覆盖字段=glue_code | 覆盖值=AH | 条件=关键词:无卤素板 | 状态=可执行草稿</t>
+          <t>字段=胶系 | 目标=胶系代码 | 覆盖字段=glue_code | 覆盖值=2A | 条件=厚度:2；关键词:普通板 | 状态=可执行草稿</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>关键词:无卤素板</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr"/>
+          <t>厚度:2；关键词:普通板</t>
+        </is>
+      </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>无卤素板</t>
-        </is>
-      </c>
-      <c r="L164" t="inlineStr"/>
-      <c r="M164" t="inlineStr"/>
-      <c r="N164" t="inlineStr"/>
+          <t>普通板</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O164" t="inlineStr">
         <is>
           <t>glue_code</t>
@@ -16142,7 +15381,7 @@
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>AH</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="Q164" t="inlineStr">
@@ -16152,7 +15391,7 @@
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="S164" t="inlineStr">
@@ -16170,8 +15409,6 @@
           <t>179</t>
         </is>
       </c>
-      <c r="V164" t="inlineStr"/>
-      <c r="W164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -16186,12 +15423,12 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>105017</t>
+          <t>105011</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>益宝悦嘉</t>
+          <t>湖南鹰飞</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -16206,36 +15443,32 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>铜箔规格</t>
+          <t>胶系</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>字段=铜箔规格 | 目标=铜箔规格代码 | 覆盖字段=copper_code | 覆盖值=KKH-H-=JJ | 条件=关键词:1-/1- | 状态=可执行草稿</t>
+          <t>字段=胶系 | 目标=胶系代码 | 覆盖字段=glue_code | 覆盖值=AH | 条件=关键词:无卤素板 | 状态=可执行草稿</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>关键词:1-/1-</t>
-        </is>
-      </c>
-      <c r="J165" t="inlineStr"/>
+          <t>关键词:无卤素板</t>
+        </is>
+      </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>1-/1-</t>
-        </is>
-      </c>
-      <c r="L165" t="inlineStr"/>
-      <c r="M165" t="inlineStr"/>
-      <c r="N165" t="inlineStr"/>
+          <t>无卤素板</t>
+        </is>
+      </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>copper_code</t>
+          <t>glue_code</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>JJ</t>
+          <t>AH</t>
         </is>
       </c>
       <c r="Q165" t="inlineStr">
@@ -16260,11 +15493,9 @@
       </c>
       <c r="U165" t="inlineStr">
         <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="V165" t="inlineStr"/>
-      <c r="W165" t="inlineStr"/>
+          <t>179</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -16299,32 +15530,32 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>基板级别</t>
+          <t>铜箔规格</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=F1 | 条件=铜厚:1oz | 状态=可执行草稿</t>
+          <t>字段=铜箔规格 | 目标=铜箔规格代码 | 覆盖字段=copper_code | 覆盖值=KKH-H-=JJ | 条件=关键词:1-/1- | 状态=可执行草稿</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>铜厚:1oz</t>
-        </is>
-      </c>
-      <c r="J166" t="inlineStr"/>
-      <c r="K166" t="inlineStr"/>
-      <c r="L166" t="inlineStr"/>
-      <c r="M166" t="inlineStr"/>
-      <c r="N166" t="inlineStr"/>
+          <t>关键词:1-/1-</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>1-/1-</t>
+        </is>
+      </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>grade_code</t>
+          <t>copper_code</t>
         </is>
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>JJ</t>
         </is>
       </c>
       <c r="Q166" t="inlineStr">
@@ -16334,7 +15565,7 @@
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="S166" t="inlineStr">
@@ -16352,8 +15583,6 @@
           <t>180</t>
         </is>
       </c>
-      <c r="V166" t="inlineStr"/>
-      <c r="W166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -16363,7 +15592,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -16393,27 +15622,14 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=A2 | 条件=胶系:NY1600；关键词:NY1600 | 状态=可执行草稿</t>
+          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=F1 | 条件=铜厚:1oz | 状态=可执行草稿</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>胶系:NY1600；关键词:NY1600</t>
-        </is>
-      </c>
-      <c r="J167" t="inlineStr">
-        <is>
-          <t>NY1600</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>NY1600</t>
-        </is>
-      </c>
-      <c r="L167" t="inlineStr"/>
-      <c r="M167" t="inlineStr"/>
-      <c r="N167" t="inlineStr"/>
+          <t>铜厚:1oz</t>
+        </is>
+      </c>
       <c r="O167" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -16421,7 +15637,7 @@
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="Q167" t="inlineStr">
@@ -16431,7 +15647,7 @@
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="S167" t="inlineStr">
@@ -16449,8 +15665,11 @@
           <t>180</t>
         </is>
       </c>
-      <c r="V167" t="inlineStr"/>
-      <c r="W167" t="inlineStr"/>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>停用拆分错误的1oz宽泛规则；由NY2140+厚度&gt;=0.8+铜厚&lt;1oz完整规则执行</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -16490,27 +15709,24 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=F1 | 条件=胶系:NY2140；厚度&gt;=0.8；铜厚&lt;=1oz | 状态=可执行草稿 | 依据=特殊需求及引擎基板级别规则</t>
+          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=A2 | 条件=胶系:NY1600；关键词:NY1600 | 状态=可执行草稿</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>胶系:NY2140；厚度&gt;=0.8；铜厚&lt;=1oz</t>
+          <t>胶系:NY1600；关键词:NY1600</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>NY2140</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr"/>
-      <c r="L168" t="inlineStr"/>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>&gt;=0.8</t>
-        </is>
-      </c>
-      <c r="N168" t="inlineStr"/>
+          <t>NY1600</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>NY1600</t>
+        </is>
+      </c>
       <c r="O168" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -16518,7 +15734,7 @@
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="Q168" t="inlineStr">
@@ -16546,12 +15762,6 @@
           <t>180</t>
         </is>
       </c>
-      <c r="V168" t="inlineStr">
-        <is>
-          <t>特殊需求及引擎基板级别规则</t>
-        </is>
-      </c>
-      <c r="W168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -16566,12 +15776,12 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>103996</t>
+          <t>105017</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>深三德盈</t>
+          <t>益宝悦嘉</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -16591,19 +15801,29 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=F1 | 条件=铜厚:1oz | 状态=可执行草稿</t>
+          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=F1 | 条件=胶系:NY2140；厚度&gt;=0.8；铜厚&lt;1oz | 状态=可执行草稿 | 依据=特殊需求及引擎基板级别规则</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>铜厚:1oz</t>
-        </is>
-      </c>
-      <c r="J169" t="inlineStr"/>
-      <c r="K169" t="inlineStr"/>
-      <c r="L169" t="inlineStr"/>
-      <c r="M169" t="inlineStr"/>
-      <c r="N169" t="inlineStr"/>
+          <t>胶系:NY2140；厚度&gt;=0.8；铜厚&lt;1oz</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>NY2140</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>&lt;1oz</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>&gt;=0.8</t>
+        </is>
+      </c>
       <c r="O169" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -16621,7 +15841,7 @@
       </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="S169" t="inlineStr">
@@ -16636,11 +15856,14 @@
       </c>
       <c r="U169" t="inlineStr">
         <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="V169" t="inlineStr"/>
-      <c r="W169" t="inlineStr"/>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>特殊需求及引擎基板级别规则；业务确认：1oz以下不包含1oz</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -16650,7 +15873,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -16680,27 +15903,14 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=F1 | 条件=胶系:NY2140；厚度&gt;=0.8；铜厚&lt;=1oz | 状态=可执行草稿 | 依据=特殊需求及引擎基板级别规则</t>
+          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=F1 | 条件=铜厚:1oz | 状态=可执行草稿</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>胶系:NY2140；厚度&gt;=0.8；铜厚&lt;=1oz</t>
-        </is>
-      </c>
-      <c r="J170" t="inlineStr">
-        <is>
-          <t>NY2140</t>
-        </is>
-      </c>
-      <c r="K170" t="inlineStr"/>
-      <c r="L170" t="inlineStr"/>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>&gt;=0.8</t>
-        </is>
-      </c>
-      <c r="N170" t="inlineStr"/>
+          <t>铜厚:1oz</t>
+        </is>
+      </c>
       <c r="O170" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -16718,7 +15928,7 @@
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="S170" t="inlineStr">
@@ -16736,12 +15946,11 @@
           <t>181</t>
         </is>
       </c>
-      <c r="V170" t="inlineStr">
-        <is>
-          <t>特殊需求及引擎基板级别规则</t>
-        </is>
-      </c>
-      <c r="W170" t="inlineStr"/>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>停用拆分错误的1oz宽泛规则；由NY2140+厚度&gt;=0.8+铜厚&lt;1oz完整规则执行</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -16756,12 +15965,12 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>103295、 103692、 123063、 123054、 103385、 123108</t>
+          <t>103996</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>科翔集团</t>
+          <t>深三德盈</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -16781,27 +15990,29 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=AD | 条件=胶系:NY3150HF；关键词:NY3150HF | 状态=可执行草稿</t>
+          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=F1 | 条件=胶系:NY2140；厚度&gt;=0.8；铜厚&lt;1oz | 状态=可执行草稿 | 依据=特殊需求及引擎基板级别规则</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>胶系:NY3150HF；关键词:NY3150HF</t>
+          <t>胶系:NY2140；厚度&gt;=0.8；铜厚&lt;1oz</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>NY3150HF</t>
-        </is>
-      </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>NY3150HF</t>
-        </is>
-      </c>
-      <c r="L171" t="inlineStr"/>
-      <c r="M171" t="inlineStr"/>
-      <c r="N171" t="inlineStr"/>
+          <t>NY2140</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>&lt;1oz</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>&gt;=0.8</t>
+        </is>
+      </c>
       <c r="O171" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -16809,7 +16020,7 @@
       </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>AD</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="Q171" t="inlineStr">
@@ -16834,11 +16045,14 @@
       </c>
       <c r="U171" t="inlineStr">
         <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="V171" t="inlineStr"/>
-      <c r="W171" t="inlineStr"/>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>特殊需求及引擎基板级别规则；业务确认：1oz以下不包含1oz</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -16878,27 +16092,24 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=AC | 条件=关键词:NY-A1 | 状态=可执行草稿</t>
+          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=AD | 条件=胶系:NY3150HF；关键词:NY3150HF | 状态=可执行草稿</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>关键词:NY-A1</t>
+          <t>胶系:NY3150HF；关键词:NY3150HF</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>NY-A1</t>
+          <t>NY3150HF</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>NY-A1</t>
-        </is>
-      </c>
-      <c r="L172" t="inlineStr"/>
-      <c r="M172" t="inlineStr"/>
-      <c r="N172" t="inlineStr"/>
+          <t>NY3150HF</t>
+        </is>
+      </c>
       <c r="O172" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -16906,7 +16117,7 @@
       </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="Q172" t="inlineStr">
@@ -16934,8 +16145,6 @@
           <t>184</t>
         </is>
       </c>
-      <c r="V172" t="inlineStr"/>
-      <c r="W172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -16975,27 +16184,24 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=AC | 条件=关键词:NY-A2 | 状态=可执行草稿</t>
+          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=AC | 条件=关键词:NY-A1 | 状态=可执行草稿</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>关键词:NY-A2</t>
+          <t>关键词:NY-A1</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>NY-A2</t>
+          <t>NY-A1</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>NY-A2</t>
-        </is>
-      </c>
-      <c r="L173" t="inlineStr"/>
-      <c r="M173" t="inlineStr"/>
-      <c r="N173" t="inlineStr"/>
+          <t>NY-A1</t>
+        </is>
+      </c>
       <c r="O173" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -17031,8 +16237,6 @@
           <t>184</t>
         </is>
       </c>
-      <c r="V173" t="inlineStr"/>
-      <c r="W173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -17047,12 +16251,12 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>103990、 103984、 123016、 123103</t>
+          <t>103295、 103692、 123063、 123054、 103385、 123108</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>广华升鑫、深华升鑫</t>
+          <t>科翔集团</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -17067,12 +16271,12 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>胶系</t>
+          <t>基板级别</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>字段=胶系 | 目标=胶系代码 | 覆盖字段=glue_code | 覆盖值=AL | 条件=关键词:NY-A2 | 状态=可执行草稿</t>
+          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=AC | 条件=关键词:NY-A2 | 状态=可执行草稿</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -17090,17 +16294,14 @@
           <t>NY-A2</t>
         </is>
       </c>
-      <c r="L174" t="inlineStr"/>
-      <c r="M174" t="inlineStr"/>
-      <c r="N174" t="inlineStr"/>
       <c r="O174" t="inlineStr">
         <is>
-          <t>glue_code</t>
+          <t>grade_code</t>
         </is>
       </c>
       <c r="P174" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="Q174" t="inlineStr">
@@ -17125,11 +16326,9 @@
       </c>
       <c r="U174" t="inlineStr">
         <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="V174" t="inlineStr"/>
-      <c r="W174" t="inlineStr"/>
+          <t>184</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -17164,17 +16363,17 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>基板级别</t>
+          <t>胶系</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=NY-A2时=AC | 条件=关键词:当胶系 | 状态=可执行草稿</t>
+          <t>字段=胶系 | 目标=胶系代码 | 覆盖字段=glue_code | 覆盖值=AL | 条件=关键词:NY-A2 | 状态=可执行草稿</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>关键词:当胶系</t>
+          <t>关键词:NY-A2</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -17182,18 +16381,19 @@
           <t>NY-A2</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
-      <c r="L175" t="inlineStr"/>
-      <c r="M175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>NY-A2</t>
+        </is>
+      </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>grade_code</t>
+          <t>glue_code</t>
         </is>
       </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="Q175" t="inlineStr">
@@ -17203,7 +16403,7 @@
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="S175" t="inlineStr">
@@ -17221,8 +16421,6 @@
           <t>185</t>
         </is>
       </c>
-      <c r="V175" t="inlineStr"/>
-      <c r="W175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -17237,12 +16435,12 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>122013</t>
+          <t>103990、 103984、 123016、 123103</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>湖北健鼎</t>
+          <t>广华升鑫、深华升鑫</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -17262,19 +16460,19 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=AT | 条件=规格中带TFT字样 | 状态=可执行草稿</t>
+          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=NY-A2时=AC | 条件=关键词:当胶系 | 状态=可执行草稿</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>规格中带TFT字样</t>
-        </is>
-      </c>
-      <c r="J176" t="inlineStr"/>
-      <c r="K176" t="inlineStr"/>
-      <c r="L176" t="inlineStr"/>
-      <c r="M176" t="inlineStr"/>
-      <c r="N176" t="inlineStr"/>
+          <t>关键词:当胶系</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>NY-A2</t>
+        </is>
+      </c>
       <c r="O176" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -17282,7 +16480,7 @@
       </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="Q176" t="inlineStr">
@@ -17292,7 +16490,7 @@
       </c>
       <c r="R176" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="S176" t="inlineStr">
@@ -17307,11 +16505,9 @@
       </c>
       <c r="U176" t="inlineStr">
         <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="V176" t="inlineStr"/>
-      <c r="W176" t="inlineStr"/>
+          <t>185</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -17326,12 +16522,12 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>104312</t>
+          <t>122013</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>无锡健鼎</t>
+          <t>湖北健鼎</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -17359,11 +16555,6 @@
           <t>规格中带TFT字样</t>
         </is>
       </c>
-      <c r="J177" t="inlineStr"/>
-      <c r="K177" t="inlineStr"/>
-      <c r="L177" t="inlineStr"/>
-      <c r="M177" t="inlineStr"/>
-      <c r="N177" t="inlineStr"/>
       <c r="O177" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -17396,11 +16587,9 @@
       </c>
       <c r="U177" t="inlineStr">
         <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="V177" t="inlineStr"/>
-      <c r="W177" t="inlineStr"/>
+          <t>189</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -17415,12 +16604,12 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>122021</t>
+          <t>104312</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>黄石广合</t>
+          <t>无锡健鼎</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -17440,27 +16629,14 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=NY2150且厚度=43MIL且结构=6*7628时=AT | 条件=胶系:NY2150；厚度:2150；关键词:当胶系 | 状态=可执行草稿</t>
+          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=AT | 条件=规格中带TFT字样 | 状态=可执行草稿</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>胶系:NY2150；厚度:2150；关键词:当胶系</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr">
-        <is>
-          <t>NY2150</t>
-        </is>
-      </c>
-      <c r="K178" t="inlineStr"/>
-      <c r="L178" t="inlineStr"/>
-      <c r="M178" t="inlineStr">
-        <is>
-          <t>2150/43MIL</t>
-        </is>
-      </c>
-      <c r="N178" t="inlineStr"/>
+          <t>规格中带TFT字样</t>
+        </is>
+      </c>
       <c r="O178" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -17478,7 +16654,7 @@
       </c>
       <c r="R178" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="S178" t="inlineStr">
@@ -17493,11 +16669,9 @@
       </c>
       <c r="U178" t="inlineStr">
         <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="V178" t="inlineStr"/>
-      <c r="W178" t="inlineStr"/>
+          <t>191</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -17512,12 +16686,12 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>123057</t>
+          <t>122021</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>江西旭昇</t>
+          <t>黄石广合</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -17532,40 +16706,37 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>胶系</t>
+          <t>基板级别</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>字段=胶系 | 目标=胶系代码 | 覆盖字段=glue_code | 覆盖值=AH | 条件=胶系:NY3150HF；关键词:NY3150HF | 状态=可执行草稿</t>
+          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=NY2150且厚度=43MIL且结构=6*7628时=AT | 条件=胶系:NY2150；厚度:2150；关键词:当胶系 | 状态=可执行草稿</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>胶系:NY3150HF；关键词:NY3150HF</t>
+          <t>胶系:NY2150；厚度:2150；关键词:当胶系</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>NY3150HF</t>
-        </is>
-      </c>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t>NY3150HF</t>
-        </is>
-      </c>
-      <c r="L179" t="inlineStr"/>
-      <c r="M179" t="inlineStr"/>
-      <c r="N179" t="inlineStr"/>
+          <t>NY2150</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>2150/43MIL</t>
+        </is>
+      </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>glue_code</t>
+          <t>grade_code</t>
         </is>
       </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>AH</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="Q179" t="inlineStr">
@@ -17590,11 +16761,9 @@
       </c>
       <c r="U179" t="inlineStr">
         <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="V179" t="inlineStr"/>
-      <c r="W179" t="inlineStr"/>
+          <t>196</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -17609,12 +16778,12 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>103786</t>
+          <t>123057</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>惠州泰和</t>
+          <t>江西旭昇</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -17629,36 +16798,37 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>基板级别</t>
+          <t>胶系</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=AT | 条件=关键词:2（含）含铜以下 | 状态=可执行草稿</t>
+          <t>字段=胶系 | 目标=胶系代码 | 覆盖字段=glue_code | 覆盖值=AH | 条件=胶系:NY3150HF；关键词:NY3150HF | 状态=可执行草稿</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>关键词:2（含）含铜以下</t>
-        </is>
-      </c>
-      <c r="J180" t="inlineStr"/>
+          <t>胶系:NY3150HF；关键词:NY3150HF</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>NY3150HF</t>
+        </is>
+      </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>2（含）含铜以下</t>
-        </is>
-      </c>
-      <c r="L180" t="inlineStr"/>
-      <c r="M180" t="inlineStr"/>
-      <c r="N180" t="inlineStr"/>
+          <t>NY3150HF</t>
+        </is>
+      </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>grade_code</t>
+          <t>glue_code</t>
         </is>
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>AH</t>
         </is>
       </c>
       <c r="Q180" t="inlineStr">
@@ -17668,7 +16838,7 @@
       </c>
       <c r="R180" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="S180" t="inlineStr">
@@ -17683,11 +16853,9 @@
       </c>
       <c r="U180" t="inlineStr">
         <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="V180" t="inlineStr"/>
-      <c r="W180" t="inlineStr"/>
+          <t>200</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -17717,33 +16885,29 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>规则来源说明</t>
+          <t>CCL特殊规则</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>业务反馈复核</t>
+          <t>基板级别</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>业务反馈：意思是总厚1.2（含）以下就等于AT</t>
+          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=AT | 条件=关键词:2（含）含铜以下 | 状态=可执行草稿</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>厚度:&lt;=1.2</t>
-        </is>
-      </c>
-      <c r="J181" t="inlineStr"/>
-      <c r="K181" t="inlineStr"/>
-      <c r="L181" t="inlineStr"/>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>&lt;=1.2</t>
-        </is>
-      </c>
-      <c r="N181" t="inlineStr"/>
+          <t>关键词:2（含）含铜以下</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>2（含）含铜以下</t>
+        </is>
+      </c>
       <c r="O181" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -17756,12 +16920,12 @@
       </c>
       <c r="Q181" t="inlineStr">
         <is>
-          <t>客户特殊规则确认草稿/业务反馈复核</t>
+          <t>客户特殊规则确认草稿</t>
         </is>
       </c>
       <c r="R181" t="inlineStr">
         <is>
-          <t>1160</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="S181" t="inlineStr">
@@ -17779,12 +16943,6 @@
           <t>203</t>
         </is>
       </c>
-      <c r="V181" t="inlineStr">
-        <is>
-          <t>由业务反馈复核行补充生成</t>
-        </is>
-      </c>
-      <c r="W181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -17799,12 +16957,12 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>103576</t>
+          <t>103786</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>珠海乐健</t>
+          <t>惠州泰和</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -17814,25 +16972,29 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>CCL特殊规则</t>
+          <t>规则来源说明</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>基板级别</t>
+          <t>业务反馈复核</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>乐健CCL基板默认下汽车板</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr"/>
-      <c r="J182" t="inlineStr"/>
-      <c r="K182" t="inlineStr"/>
-      <c r="L182" t="inlineStr"/>
-      <c r="M182" t="inlineStr"/>
-      <c r="N182" t="inlineStr"/>
+          <t>业务反馈：意思是总厚1.2（含）以下就等于AT</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>厚度:&lt;=1.2</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>&lt;=1.2</t>
+        </is>
+      </c>
       <c r="O182" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -17840,17 +17002,17 @@
       </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="Q182" t="inlineStr">
         <is>
-          <t>客户特殊规则确认草稿/原始CCL确定性解析</t>
+          <t>客户特殊规则确认草稿/业务反馈复核</t>
         </is>
       </c>
       <c r="R182" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>1160</t>
         </is>
       </c>
       <c r="S182" t="inlineStr">
@@ -17865,15 +17027,14 @@
       </c>
       <c r="U182" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>203</t>
         </is>
       </c>
       <c r="V182" t="inlineStr">
         <is>
-          <t>业务反馈确认PP不考虑，仅按CCL基板汽车板/非汽车板条件执行</t>
-        </is>
-      </c>
-      <c r="W182" t="inlineStr"/>
+          <t>由业务反馈复核行补充生成</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -17913,27 +17074,9 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>NY2150 板厚1.1mm 全部下非汽车板</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>胶系:NY2150；厚度:1.1</t>
-        </is>
-      </c>
-      <c r="J183" t="inlineStr">
-        <is>
-          <t>NY2150</t>
-        </is>
-      </c>
-      <c r="K183" t="inlineStr"/>
-      <c r="L183" t="inlineStr"/>
-      <c r="M183" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="N183" t="inlineStr"/>
+          <t>乐健CCL基板默认下汽车板</t>
+        </is>
+      </c>
       <c r="O183" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -17941,7 +17084,7 @@
       </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="Q183" t="inlineStr">
@@ -17951,7 +17094,7 @@
       </c>
       <c r="R183" t="inlineStr">
         <is>
-          <t>1150</t>
+          <t>1080</t>
         </is>
       </c>
       <c r="S183" t="inlineStr">
@@ -17974,7 +17117,6 @@
           <t>业务反馈确认PP不考虑，仅按CCL基板汽车板/非汽车板条件执行</t>
         </is>
       </c>
-      <c r="W183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -18014,12 +17156,12 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>NY2150 板厚1.5/1.45mm 且铜厚H/H、1/1、2/2全部下非汽车板</t>
+          <t>NY2150 板厚1.1mm 全部下非汽车板</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>胶系:NY2150；厚度:1.5/1.45；铜厚:H/H,1/1,2/2</t>
+          <t>胶系:NY2150；厚度:1.1</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -18027,18 +17169,11 @@
           <t>NY2150</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
-      <c r="L184" t="inlineStr">
-        <is>
-          <t>H/H,1/1,2/2</t>
-        </is>
-      </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>1.5/1.45</t>
-        </is>
-      </c>
-      <c r="N184" t="inlineStr"/>
+          <t>1.1</t>
+        </is>
+      </c>
       <c r="O184" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -18056,7 +17191,7 @@
       </c>
       <c r="R184" t="inlineStr">
         <is>
-          <t>1160</t>
+          <t>1150</t>
         </is>
       </c>
       <c r="S184" t="inlineStr">
@@ -18079,7 +17214,6 @@
           <t>业务反馈确认PP不考虑，仅按CCL基板汽车板/非汽车板条件执行</t>
         </is>
       </c>
-      <c r="W184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -18094,12 +17228,12 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>123123</t>
+          <t>103576</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>赣州乐健</t>
+          <t>珠海乐健</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -18119,15 +17253,29 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>乐健CCL基板默认下汽车板</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr"/>
-      <c r="J185" t="inlineStr"/>
-      <c r="K185" t="inlineStr"/>
-      <c r="L185" t="inlineStr"/>
-      <c r="M185" t="inlineStr"/>
-      <c r="N185" t="inlineStr"/>
+          <t>NY2150 板厚1.5/1.45mm 且铜厚H/H、1/1、2/2全部下非汽车板</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>胶系:NY2150；厚度:1.5/1.45；铜厚:H/H,1/1,2/2</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>NY2150</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>H/H,1/1,2/2</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>1.5/1.45</t>
+        </is>
+      </c>
       <c r="O185" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -18135,7 +17283,7 @@
       </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="Q185" t="inlineStr">
@@ -18145,7 +17293,7 @@
       </c>
       <c r="R185" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>1160</t>
         </is>
       </c>
       <c r="S185" t="inlineStr">
@@ -18160,7 +17308,7 @@
       </c>
       <c r="U185" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>206</t>
         </is>
       </c>
       <c r="V185" t="inlineStr">
@@ -18168,7 +17316,6 @@
           <t>业务反馈确认PP不考虑，仅按CCL基板汽车板/非汽车板条件执行</t>
         </is>
       </c>
-      <c r="W185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -18208,27 +17355,9 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>NY2150 板厚1.1mm 全部下非汽车板</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>胶系:NY2150；厚度:1.1</t>
-        </is>
-      </c>
-      <c r="J186" t="inlineStr">
-        <is>
-          <t>NY2150</t>
-        </is>
-      </c>
-      <c r="K186" t="inlineStr"/>
-      <c r="L186" t="inlineStr"/>
-      <c r="M186" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="N186" t="inlineStr"/>
+          <t>乐健CCL基板默认下汽车板</t>
+        </is>
+      </c>
       <c r="O186" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -18236,7 +17365,7 @@
       </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="Q186" t="inlineStr">
@@ -18246,7 +17375,7 @@
       </c>
       <c r="R186" t="inlineStr">
         <is>
-          <t>1150</t>
+          <t>1080</t>
         </is>
       </c>
       <c r="S186" t="inlineStr">
@@ -18269,7 +17398,6 @@
           <t>业务反馈确认PP不考虑，仅按CCL基板汽车板/非汽车板条件执行</t>
         </is>
       </c>
-      <c r="W186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -18309,12 +17437,12 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>NY2150 板厚1.5/1.45mm 且铜厚H/H、1/1、2/2全部下非汽车板</t>
+          <t>NY2150 板厚1.1mm 全部下非汽车板</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>胶系:NY2150；厚度:1.5/1.45；铜厚:H/H,1/1,2/2</t>
+          <t>胶系:NY2150；厚度:1.1</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -18322,18 +17450,11 @@
           <t>NY2150</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
-      <c r="L187" t="inlineStr">
-        <is>
-          <t>H/H,1/1,2/2</t>
-        </is>
-      </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>1.5/1.45</t>
-        </is>
-      </c>
-      <c r="N187" t="inlineStr"/>
+          <t>1.1</t>
+        </is>
+      </c>
       <c r="O187" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -18351,7 +17472,7 @@
       </c>
       <c r="R187" t="inlineStr">
         <is>
-          <t>1160</t>
+          <t>1150</t>
         </is>
       </c>
       <c r="S187" t="inlineStr">
@@ -18374,7 +17495,6 @@
           <t>业务反馈确认PP不考虑，仅按CCL基板汽车板/非汽车板条件执行</t>
         </is>
       </c>
-      <c r="W187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -18389,12 +17509,12 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>104196</t>
+          <t>123123</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>昆山华兴</t>
+          <t>赣州乐健</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -18414,27 +17534,29 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=F1 | 条件=胶系:NY2140；关键词:NY2140 | 状态=可执行草稿</t>
+          <t>NY2150 板厚1.5/1.45mm 且铜厚H/H、1/1、2/2全部下非汽车板</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>胶系:NY2140；关键词:NY2140</t>
+          <t>胶系:NY2150；厚度:1.5/1.45；铜厚:H/H,1/1,2/2</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>NY2140</t>
-        </is>
-      </c>
-      <c r="K188" t="inlineStr">
-        <is>
-          <t>NY2140</t>
-        </is>
-      </c>
-      <c r="L188" t="inlineStr"/>
-      <c r="M188" t="inlineStr"/>
-      <c r="N188" t="inlineStr"/>
+          <t>NY2150</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>H/H,1/1,2/2</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>1.5/1.45</t>
+        </is>
+      </c>
       <c r="O188" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -18442,17 +17564,17 @@
       </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="Q188" t="inlineStr">
         <is>
-          <t>客户特殊规则确认草稿</t>
+          <t>客户特殊规则确认草稿/原始CCL确定性解析</t>
         </is>
       </c>
       <c r="R188" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1160</t>
         </is>
       </c>
       <c r="S188" t="inlineStr">
@@ -18467,11 +17589,14 @@
       </c>
       <c r="U188" t="inlineStr">
         <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="V188" t="inlineStr"/>
-      <c r="W188" t="inlineStr"/>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="V188" t="inlineStr">
+        <is>
+          <t>业务反馈确认PP不考虑，仅按CCL基板汽车板/非汽车板条件执行</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -18486,12 +17611,12 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>157001</t>
+          <t>104196</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>泰国景旺</t>
+          <t>昆山华兴</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -18506,36 +17631,37 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>铜箔类型+印字/非印字</t>
+          <t>基板级别</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>字段=铜箔类型+印字/非印字 | 目标=铜箔类型/印字代码 | 覆盖字段=copper_type_code | 覆盖值=O(HVLP1) | 条件=关键词:HVLP | 状态=可执行草稿</t>
+          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=F1 | 条件=胶系:NY2140；关键词:NY2140 | 状态=可执行草稿</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>关键词:HVLP</t>
-        </is>
-      </c>
-      <c r="J189" t="inlineStr"/>
+          <t>胶系:NY2140；关键词:NY2140</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>NY2140</t>
+        </is>
+      </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>HVLP</t>
-        </is>
-      </c>
-      <c r="L189" t="inlineStr"/>
-      <c r="M189" t="inlineStr"/>
-      <c r="N189" t="inlineStr"/>
+          <t>NY2140</t>
+        </is>
+      </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>copper_type_code</t>
+          <t>grade_code</t>
         </is>
       </c>
       <c r="P189" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="Q189" t="inlineStr">
@@ -18545,7 +17671,7 @@
       </c>
       <c r="R189" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="S189" t="inlineStr">
@@ -18560,11 +17686,9 @@
       </c>
       <c r="U189" t="inlineStr">
         <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="V189" t="inlineStr"/>
-      <c r="W189" t="inlineStr"/>
+          <t>210</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -18599,36 +17723,32 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>基板级别</t>
+          <t>铜箔类型+印字/非印字</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=A1 | 条件=胶系:NY3150HC；关键词:当胶系 ；胶系代码:RV| 状态=可执行草稿</t>
+          <t>字段=铜箔类型+印字/非印字 | 目标=铜箔类型/印字代码 | 覆盖字段=copper_type_code | 覆盖值=O(HVLP1) | 条件=关键词:HVLP | 状态=可执行草稿</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>胶系:NY3150HC；关键词:当胶系 ；胶系代码:RV</t>
-        </is>
-      </c>
-      <c r="J190" t="inlineStr">
-        <is>
-          <t>NY3150HC</t>
-        </is>
-      </c>
-      <c r="K190" t="inlineStr"/>
-      <c r="L190" t="inlineStr"/>
-      <c r="M190" t="inlineStr"/>
-      <c r="N190" t="inlineStr"/>
+          <t>关键词:HVLP</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>HVLP</t>
+        </is>
+      </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>grade_code</t>
+          <t>copper_type_code</t>
         </is>
       </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>O</t>
         </is>
       </c>
       <c r="Q190" t="inlineStr">
@@ -18638,7 +17758,7 @@
       </c>
       <c r="R190" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="S190" t="inlineStr">
@@ -18656,8 +17776,6 @@
           <t>211</t>
         </is>
       </c>
-      <c r="V190" t="inlineStr"/>
-      <c r="W190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -18697,23 +17815,19 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=NY2150H时=AP | 条件=胶系:NY2150H；关键词:当胶系 | 状态=可执行草稿</t>
+          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=A1 | 条件=胶系:NY3150HC；关键词:当胶系 ；胶系代码:RV| 状态=可执行草稿</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>胶系:NY2150H；关键词:当胶系</t>
+          <t>胶系:NY3150HC；关键词:当胶系 ；胶系代码:RV</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>NY2150H</t>
-        </is>
-      </c>
-      <c r="K191" t="inlineStr"/>
-      <c r="L191" t="inlineStr"/>
-      <c r="M191" t="inlineStr"/>
-      <c r="N191" t="inlineStr"/>
+          <t>NY3150HC</t>
+        </is>
+      </c>
       <c r="O191" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -18721,7 +17835,7 @@
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="Q191" t="inlineStr">
@@ -18749,8 +17863,6 @@
           <t>211</t>
         </is>
       </c>
-      <c r="V191" t="inlineStr"/>
-      <c r="W191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -18790,23 +17902,19 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=AC | 条件=胶系:NY-A1 | 状态=可执行草稿 | 依据=特殊需求多条件同结果</t>
+          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=NY2150H时=AP | 条件=胶系:NY2150H；关键词:当胶系 | 状态=可执行草稿</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>胶系:NY-A1</t>
+          <t>胶系:NY2150H；关键词:当胶系</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>NY-A1</t>
-        </is>
-      </c>
-      <c r="K192" t="inlineStr"/>
-      <c r="L192" t="inlineStr"/>
-      <c r="M192" t="inlineStr"/>
-      <c r="N192" t="inlineStr"/>
+          <t>NY2150H</t>
+        </is>
+      </c>
       <c r="O192" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -18814,7 +17922,7 @@
       </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="Q192" t="inlineStr">
@@ -18842,12 +17950,6 @@
           <t>211</t>
         </is>
       </c>
-      <c r="V192" t="inlineStr">
-        <is>
-          <t>特殊需求多条件同结果</t>
-        </is>
-      </c>
-      <c r="W192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -18887,23 +17989,19 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=AC | 条件=胶系:NY-A2 | 状态=可执行草稿 | 依据=特殊需求多条件同结果</t>
+          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=AC | 条件=胶系:NY-A1 | 状态=可执行草稿 | 依据=特殊需求多条件同结果</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>胶系:NY-A2</t>
+          <t>胶系:NY-A1</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>NY-A2</t>
-        </is>
-      </c>
-      <c r="K193" t="inlineStr"/>
-      <c r="L193" t="inlineStr"/>
-      <c r="M193" t="inlineStr"/>
-      <c r="N193" t="inlineStr"/>
+          <t>NY-A1</t>
+        </is>
+      </c>
       <c r="O193" t="inlineStr">
         <is>
           <t>grade_code</t>
@@ -18944,7 +18042,6 @@
           <t>特殊需求多条件同结果</t>
         </is>
       </c>
-      <c r="W193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -18974,45 +18071,37 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>通用特殊规则</t>
+          <t>CCL特殊规则</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>胶系</t>
+          <t>基板级别</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>字段=胶系 | 目标=胶系代码 | 覆盖字段=glue_code | 覆盖值=2B | 条件=胶系:NY2150；关键词:NY2150 | 状态=可执行草稿</t>
+          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=AC | 条件=胶系:NY-A2 | 状态=可执行草稿 | 依据=特殊需求多条件同结果</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>胶系:NY2150；关键词:NY2150</t>
+          <t>胶系:NY-A2</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>NY2150</t>
-        </is>
-      </c>
-      <c r="K194" t="inlineStr">
-        <is>
-          <t>NY2150</t>
-        </is>
-      </c>
-      <c r="L194" t="inlineStr"/>
-      <c r="M194" t="inlineStr"/>
-      <c r="N194" t="inlineStr"/>
+          <t>NY-A2</t>
+        </is>
+      </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>glue_code</t>
+          <t>grade_code</t>
         </is>
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="Q194" t="inlineStr">
@@ -19022,7 +18111,7 @@
       </c>
       <c r="R194" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="S194" t="inlineStr">
@@ -19040,8 +18129,11 @@
           <t>211</t>
         </is>
       </c>
-      <c r="V194" t="inlineStr"/>
-      <c r="W194" t="inlineStr"/>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>特殊需求多条件同结果</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -19056,12 +18148,12 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>103844</t>
+          <t>157001</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>万安裕维</t>
+          <t>泰国景旺</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -19071,7 +18163,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>CCL特殊规则</t>
+          <t>通用特殊规则</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -19081,23 +18173,24 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>字段=胶系 | 目标=胶系代码 | 覆盖字段=glue_code | 覆盖值=2B | 条件=关键词:TG150 | 状态=可执行草稿</t>
+          <t>字段=胶系 | 目标=胶系代码 | 覆盖字段=glue_code | 覆盖值=2B | 条件=胶系:NY2150；关键词:NY2150 | 状态=可执行草稿</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>关键词:TG150</t>
-        </is>
-      </c>
-      <c r="J195" t="inlineStr"/>
+          <t>胶系:NY2150；关键词:NY2150</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>NY2150</t>
+        </is>
+      </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>TG150</t>
-        </is>
-      </c>
-      <c r="L195" t="inlineStr"/>
-      <c r="M195" t="inlineStr"/>
-      <c r="N195" t="inlineStr"/>
+          <t>NY2150</t>
+        </is>
+      </c>
       <c r="O195" t="inlineStr">
         <is>
           <t>glue_code</t>
@@ -19115,7 +18208,7 @@
       </c>
       <c r="R195" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>950</t>
         </is>
       </c>
       <c r="S195" t="inlineStr">
@@ -19130,11 +18223,9 @@
       </c>
       <c r="U195" t="inlineStr">
         <is>
-          <t>213</t>
-        </is>
-      </c>
-      <c r="V195" t="inlineStr"/>
-      <c r="W195" t="inlineStr"/>
+          <t>211</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -19174,23 +18265,19 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>字段=胶系 | 目标=胶系代码 | 覆盖字段=glue_code | 覆盖值=3B | 条件=关键词:TG150和无卤素 | 状态=可执行草稿</t>
+          <t>字段=胶系 | 目标=胶系代码 | 覆盖字段=glue_code | 覆盖值=2B | 条件=关键词:TG150 | 状态=可执行草稿</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>关键词:TG150和无卤素</t>
-        </is>
-      </c>
-      <c r="J196" t="inlineStr"/>
+          <t>关键词:TG150</t>
+        </is>
+      </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>TG150和无卤素</t>
-        </is>
-      </c>
-      <c r="L196" t="inlineStr"/>
-      <c r="M196" t="inlineStr"/>
-      <c r="N196" t="inlineStr"/>
+          <t>TG150</t>
+        </is>
+      </c>
       <c r="O196" t="inlineStr">
         <is>
           <t>glue_code</t>
@@ -19198,7 +18285,7 @@
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="Q196" t="inlineStr">
@@ -19208,7 +18295,7 @@
       </c>
       <c r="R196" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="S196" t="inlineStr">
@@ -19226,8 +18313,6 @@
           <t>213</t>
         </is>
       </c>
-      <c r="V196" t="inlineStr"/>
-      <c r="W196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -19267,23 +18352,19 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>字段=胶系 | 目标=胶系代码 | 覆盖字段=glue_code | 覆盖值=3H | 条件=关键词:TG150&amp;无卤素&amp;CTI600 | 状态=可执行草稿</t>
+          <t>字段=胶系 | 目标=胶系代码 | 覆盖字段=glue_code | 覆盖值=3B | 条件=关键词:TG150和无卤素 | 状态=可执行草稿</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>关键词:TG150&amp;无卤素&amp;CTI600</t>
-        </is>
-      </c>
-      <c r="J197" t="inlineStr"/>
+          <t>关键词:TG150和无卤素</t>
+        </is>
+      </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>TG150&amp;无卤素&amp;CTI600</t>
-        </is>
-      </c>
-      <c r="L197" t="inlineStr"/>
-      <c r="M197" t="inlineStr"/>
-      <c r="N197" t="inlineStr"/>
+          <t>TG150和无卤素</t>
+        </is>
+      </c>
       <c r="O197" t="inlineStr">
         <is>
           <t>glue_code</t>
@@ -19291,7 +18372,7 @@
       </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>3H</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="Q197" t="inlineStr">
@@ -19301,7 +18382,7 @@
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="S197" t="inlineStr">
@@ -19319,8 +18400,6 @@
           <t>213</t>
         </is>
       </c>
-      <c r="V197" t="inlineStr"/>
-      <c r="W197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -19360,23 +18439,19 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>字段=胶系 | 目标=胶系代码 | 覆盖字段=glue_code | 覆盖值=1L | 条件=关键词:TG135&amp;CTI600 | 状态=可执行草稿</t>
+          <t>字段=胶系 | 目标=胶系代码 | 覆盖字段=glue_code | 覆盖值=3H | 条件=关键词:TG150&amp;无卤素&amp;CTI600 | 状态=可执行草稿</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>关键词:TG135&amp;CTI600</t>
-        </is>
-      </c>
-      <c r="J198" t="inlineStr"/>
+          <t>关键词:TG150&amp;无卤素&amp;CTI600</t>
+        </is>
+      </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>TG135&amp;CTI600</t>
-        </is>
-      </c>
-      <c r="L198" t="inlineStr"/>
-      <c r="M198" t="inlineStr"/>
-      <c r="N198" t="inlineStr"/>
+          <t>TG150&amp;无卤素&amp;CTI600</t>
+        </is>
+      </c>
       <c r="O198" t="inlineStr">
         <is>
           <t>glue_code</t>
@@ -19384,7 +18459,7 @@
       </c>
       <c r="P198" t="inlineStr">
         <is>
-          <t>1L</t>
+          <t>3H</t>
         </is>
       </c>
       <c r="Q198" t="inlineStr">
@@ -19394,7 +18469,7 @@
       </c>
       <c r="R198" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="S198" t="inlineStr">
@@ -19412,8 +18487,6 @@
           <t>213</t>
         </is>
       </c>
-      <c r="V198" t="inlineStr"/>
-      <c r="W198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -19453,23 +18526,19 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>胶系:客户没标注TG或者TG130=2140</t>
+          <t>字段=胶系 | 目标=胶系代码 | 覆盖字段=glue_code | 覆盖值=1L | 条件=关键词:TG135&amp;CTI600 | 状态=可执行草稿</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>关键词:__NO_TG__</t>
-        </is>
-      </c>
-      <c r="J199" t="inlineStr"/>
+          <t>关键词:TG135&amp;CTI600</t>
+        </is>
+      </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>__NO_TG__</t>
-        </is>
-      </c>
-      <c r="L199" t="inlineStr"/>
-      <c r="M199" t="inlineStr"/>
-      <c r="N199" t="inlineStr"/>
+          <t>TG135&amp;CTI600</t>
+        </is>
+      </c>
       <c r="O199" t="inlineStr">
         <is>
           <t>glue_code</t>
@@ -19477,17 +18546,17 @@
       </c>
       <c r="P199" t="inlineStr">
         <is>
-          <t>2A</t>
+          <t>1L</t>
         </is>
       </c>
       <c r="Q199" t="inlineStr">
         <is>
-          <t>客户特殊规则确认草稿/原始CCL确定性解析</t>
+          <t>客户特殊规则确认草稿</t>
         </is>
       </c>
       <c r="R199" t="inlineStr">
         <is>
-          <t>1090</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="S199" t="inlineStr">
@@ -19505,12 +18574,6 @@
           <t>213</t>
         </is>
       </c>
-      <c r="V199" t="inlineStr">
-        <is>
-          <t>由原始CCL胶系TG语义规则生成</t>
-        </is>
-      </c>
-      <c r="W199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -19555,18 +18618,14 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>关键词:TG130</t>
-        </is>
-      </c>
-      <c r="J200" t="inlineStr"/>
+          <t>关键词:__NO_TG__</t>
+        </is>
+      </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>TG130</t>
-        </is>
-      </c>
-      <c r="L200" t="inlineStr"/>
-      <c r="M200" t="inlineStr"/>
-      <c r="N200" t="inlineStr"/>
+          <t>__NO_TG__</t>
+        </is>
+      </c>
       <c r="O200" t="inlineStr">
         <is>
           <t>glue_code</t>
@@ -19584,7 +18643,7 @@
       </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1090</t>
         </is>
       </c>
       <c r="S200" t="inlineStr">
@@ -19607,7 +18666,6 @@
           <t>由原始CCL胶系TG语义规则生成</t>
         </is>
       </c>
-      <c r="W200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -19622,89 +18680,695 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
+          <t>103844</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>万安裕维</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>CCL</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>CCL特殊规则</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>胶系</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>胶系:客户没标注TG或者TG130=2140</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>关键词:TG130</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>TG130</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>glue_code</t>
+        </is>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>2A</t>
+        </is>
+      </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>客户特殊规则确认草稿/原始CCL确定性解析</t>
+        </is>
+      </c>
+      <c r="R201" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>由原始CCL胶系TG语义规则生成</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>TAR-00201</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
           <t>103353</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr">
+      <c r="D202" t="inlineStr">
         <is>
           <t>清远富盈</t>
         </is>
       </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>CCL</t>
-        </is>
-      </c>
-      <c r="F201" t="inlineStr">
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>CCL</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
         <is>
           <t>CCL特殊规则</t>
         </is>
       </c>
-      <c r="G201" t="inlineStr">
+      <c r="G202" t="inlineStr">
         <is>
           <t>胶系</t>
         </is>
       </c>
-      <c r="H201" t="inlineStr">
+      <c r="H202" t="inlineStr">
         <is>
           <t>字段=胶系 | 目标=胶系代码 | 覆盖字段=glue_code | 覆盖值=2E | 条件=胶系:NY2170；关键词:NY2170&amp;5/5 | 状态=可执行草稿</t>
         </is>
       </c>
-      <c r="I201" t="inlineStr">
+      <c r="I202" t="inlineStr">
         <is>
           <t>胶系:NY2170；关键词:NY2170&amp;5/5</t>
         </is>
       </c>
-      <c r="J201" t="inlineStr">
+      <c r="J202" t="inlineStr">
         <is>
           <t>NY2170</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr">
+      <c r="K202" t="inlineStr">
         <is>
           <t>NY2170&amp;5/5</t>
         </is>
       </c>
-      <c r="L201" t="inlineStr"/>
-      <c r="M201" t="inlineStr"/>
-      <c r="N201" t="inlineStr"/>
-      <c r="O201" t="inlineStr">
+      <c r="O202" t="inlineStr">
         <is>
           <t>glue_code</t>
         </is>
       </c>
-      <c r="P201" t="inlineStr">
+      <c r="P202" t="inlineStr">
         <is>
           <t>2E</t>
         </is>
       </c>
-      <c r="Q201" t="inlineStr">
+      <c r="Q202" t="inlineStr">
         <is>
           <t>客户特殊规则确认草稿</t>
         </is>
       </c>
-      <c r="R201" t="inlineStr">
+      <c r="R202" t="inlineStr">
         <is>
           <t>1060</t>
         </is>
       </c>
-      <c r="S201" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="T201" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="U201" t="inlineStr">
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U202" t="inlineStr">
         <is>
           <t>215</t>
         </is>
       </c>
-      <c r="V201" t="inlineStr"/>
-      <c r="W201" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>TAR-CYB-20260721-001</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>103295</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>惠州智恩</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>CCL</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>CCL特殊规则</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>基板级别</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>惠州智恩且胶系=NY-A2时，基板级别=AC；胶系代码沿用基础规则</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>胶系:NY-A2</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>NY-A2</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>grade_code</t>
+        </is>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>业务反馈确认20260721</t>
+        </is>
+      </c>
+      <c r="R203" t="n">
+        <v>1100</v>
+      </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="T203" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>业务反馈20260721</t>
+        </is>
+      </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>只覆盖基板级别，不覆盖胶系代码</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>TAR-CYB-20260721-002</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>104686</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>广东依顿</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>CCL</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>CCL特殊规则</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>基板级别</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>未提供或未命中明确订单备注时，广东依顿基板级别沿用默认A1</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>grade_code</t>
+        </is>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>业务反馈确认20260721</t>
+        </is>
+      </c>
+      <c r="R204" t="n">
+        <v>900</v>
+      </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>业务反馈20260721</t>
+        </is>
+      </c>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>耐CAF/ANTI-CAF本身不代表汽车板；明确订单备注可由更高优先级规则覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>TAR-CYB-20260721-003</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>103898</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>广东喜珍</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>CCL</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>CCL特殊规则</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>基板级别</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>未提供或未命中明确订单备注时，广东喜珍基板级别沿用默认A1</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>grade_code</t>
+        </is>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>业务反馈确认20260721</t>
+        </is>
+      </c>
+      <c r="R205" t="n">
+        <v>900</v>
+      </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>业务反馈20260721</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>NY3150HF/NY2140L等明确条件及订单备注规则优先</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>TAR-CYB-20260721-004</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>广州名幸</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>CCL</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>CCL特殊规则</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>基板级别</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>广州名幸规格包含假板时，基板级别=A1</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>关键词:假板</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>假板</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>grade_code</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>业务反馈确认20260721</t>
+        </is>
+      </c>
+      <c r="R206" t="n">
+        <v>1080</v>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>业务反馈20260721</t>
+        </is>
+      </c>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>A级假板按A1；不依赖订单备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>TAR-00202</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>103683</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>鹤山中富</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>CCL</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>CCL特殊规则</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>基板级别</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=AP | 条件=关键词:当订单中客户规格没有Q时 | 状态=可执行草稿</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>关键词:当订单中客户规格没有Q时</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>当订单中客户规格没有Q时</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>grade_code</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>客户特殊规则确认草稿</t>
+        </is>
+      </c>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t>1030</t>
+        </is>
+      </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>客户规格字段缺少独立Q标识时覆盖AP；不依赖订单备注列</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>TAR-00203</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>103067</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>深圳中富</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>CCL</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>CCL特殊规则</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>基板级别</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>字段=基板级别 | 目标=基板级别代码 | 覆盖字段=grade_code | 覆盖值=AP | 条件=关键词:当订单中客户规格没有Q时 | 状态=可执行草稿</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>关键词:当订单中客户规格没有Q时</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>当订单中客户规格没有Q时</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>grade_code</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>客户特殊规则确认草稿</t>
+        </is>
+      </c>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t>1030</t>
+        </is>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="T208" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="V208" t="inlineStr">
+        <is>
+          <t>客户规格字段缺少独立Q标识时覆盖AP；不依赖订单备注列</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -19756,7 +19420,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>/Users/ny/Desktop/南亚/产品包/nanya_transcode_agent_handoff_CLEAN_20260703/nanya_marketing_os_dev/storage/rules/transcode_agent/versions/transcode_agent_rules_20260709_150049/customer_special_master.xlsx</t>
+          <t>/Users/ny/Desktop/南亚/产品包/nanya_transcode_agent_handoff_CLEAN_20260703/nanya_marketing_os_dev/storage/rules/transcode_agent/versions/transcode_agent_rules_20260720_142251/customer_special_master.xlsx</t>
         </is>
       </c>
     </row>
@@ -19767,7 +19431,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="5">
@@ -19820,7 +19484,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 15:00:49</t>
+          <t>2026-07-20 14:22:51</t>
         </is>
       </c>
     </row>
